--- a/research/traditional_assets/database/data/jordan/jordan_trucking.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_trucking.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1213959268622316</v>
+        <v>0.1211891350085072</v>
       </c>
       <c r="C2">
-        <v>30.09326734392193</v>
+        <v>29.88869930418212</v>
       </c>
       <c r="D2">
-        <v>29.68726734392193</v>
+        <v>29.76869930418212</v>
       </c>
       <c r="E2">
-        <v>-12.7</v>
+        <v>-12.414</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.286</v>
       </c>
       <c r="G2">
         <v>0.406</v>
@@ -1579,28 +1579,28 @@
         <v>4.91</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0143858</v>
       </c>
       <c r="N2">
-        <v>4.91</v>
+        <v>4.8956142</v>
       </c>
       <c r="O2">
-        <v>0.9820000000000001</v>
+        <v>0.97912284</v>
       </c>
       <c r="P2">
-        <v>3.928</v>
+        <v>3.91649136</v>
       </c>
       <c r="Q2">
-        <v>8.617999999999999</v>
+        <v>8.60649136</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1213959268622316</v>
+        <v>0.1220068030388961</v>
       </c>
       <c r="T2">
-        <v>0.8278063840919478</v>
+        <v>0.8344957286098627</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>341.3087906129655</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1211891350085072</v>
+        <v>0.1209823431547827</v>
       </c>
       <c r="C3">
-        <v>29.88869930418212</v>
+        <v>29.68457922776211</v>
       </c>
       <c r="D3">
-        <v>29.76869930418212</v>
+        <v>29.85057922776211</v>
       </c>
       <c r="E3">
-        <v>-12.414</v>
+        <v>-12.128</v>
       </c>
       <c r="F3">
-        <v>0.286</v>
+        <v>0.5720000000000001</v>
       </c>
       <c r="G3">
         <v>0.406</v>
@@ -1661,28 +1661,28 @@
         <v>4.91</v>
       </c>
       <c r="M3">
-        <v>0.0143858</v>
+        <v>0.0287716</v>
       </c>
       <c r="N3">
-        <v>4.8956142</v>
+        <v>4.8812284</v>
       </c>
       <c r="O3">
-        <v>0.97912284</v>
+        <v>0.9762456800000001</v>
       </c>
       <c r="P3">
-        <v>3.91649136</v>
+        <v>3.90498272</v>
       </c>
       <c r="Q3">
-        <v>8.60649136</v>
+        <v>8.594982720000001</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1220068030388961</v>
+        <v>0.1226301460763089</v>
       </c>
       <c r="T3">
-        <v>0.8344957286098627</v>
+        <v>0.8413215903628367</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>341.3087906129655</v>
+        <v>170.6543953064828</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1209823431547827</v>
+        <v>0.1207755513010582</v>
       </c>
       <c r="C4">
-        <v>29.68457922776211</v>
+        <v>29.48091082127679</v>
       </c>
       <c r="D4">
-        <v>29.85057922776211</v>
+        <v>29.9329108212768</v>
       </c>
       <c r="E4">
-        <v>-12.128</v>
+        <v>-11.842</v>
       </c>
       <c r="F4">
-        <v>0.5720000000000001</v>
+        <v>0.858</v>
       </c>
       <c r="G4">
         <v>0.406</v>
@@ -1743,28 +1743,28 @@
         <v>4.91</v>
       </c>
       <c r="M4">
-        <v>0.0287716</v>
+        <v>0.0431574</v>
       </c>
       <c r="N4">
-        <v>4.8812284</v>
+        <v>4.8668426</v>
       </c>
       <c r="O4">
-        <v>0.9762456800000001</v>
+        <v>0.9733685200000001</v>
       </c>
       <c r="P4">
-        <v>3.90498272</v>
+        <v>3.89347408</v>
       </c>
       <c r="Q4">
-        <v>8.594982720000001</v>
+        <v>8.583474079999998</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1226301460763089</v>
+        <v>0.1232663415474827</v>
       </c>
       <c r="T4">
-        <v>0.8413215903628367</v>
+        <v>0.8482881915333981</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>170.6543953064828</v>
+        <v>113.7695968709885</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1207755513010582</v>
+        <v>0.1205687594473338</v>
       </c>
       <c r="C5">
-        <v>29.48091082127679</v>
+        <v>29.27769783234738</v>
       </c>
       <c r="D5">
-        <v>29.9329108212768</v>
+        <v>30.01569783234738</v>
       </c>
       <c r="E5">
-        <v>-11.842</v>
+        <v>-11.556</v>
       </c>
       <c r="F5">
-        <v>0.858</v>
+        <v>1.144</v>
       </c>
       <c r="G5">
         <v>0.406</v>
@@ -1825,28 +1825,28 @@
         <v>4.91</v>
       </c>
       <c r="M5">
-        <v>0.0431574</v>
+        <v>0.0575432</v>
       </c>
       <c r="N5">
-        <v>4.8668426</v>
+        <v>4.852456800000001</v>
       </c>
       <c r="O5">
-        <v>0.9733685200000001</v>
+        <v>0.9704913600000001</v>
       </c>
       <c r="P5">
-        <v>3.89347408</v>
+        <v>3.881965440000001</v>
       </c>
       <c r="Q5">
-        <v>8.583474079999998</v>
+        <v>8.57196544</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1232663415474827</v>
+        <v>0.1239157910909727</v>
       </c>
       <c r="T5">
-        <v>0.8482881915333981</v>
+        <v>0.8553999302283462</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>113.7695968709885</v>
+        <v>85.3271976532414</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1205687594473338</v>
+        <v>0.1203619675936093</v>
       </c>
       <c r="C6">
-        <v>29.27769783234738</v>
+        <v>29.07494405017006</v>
       </c>
       <c r="D6">
-        <v>30.01569783234738</v>
+        <v>30.09894405017006</v>
       </c>
       <c r="E6">
-        <v>-11.556</v>
+        <v>-11.27</v>
       </c>
       <c r="F6">
-        <v>1.144</v>
+        <v>1.43</v>
       </c>
       <c r="G6">
         <v>0.406</v>
@@ -1907,28 +1907,28 @@
         <v>4.91</v>
       </c>
       <c r="M6">
-        <v>0.0575432</v>
+        <v>0.07192900000000001</v>
       </c>
       <c r="N6">
-        <v>4.852456800000001</v>
+        <v>4.838071</v>
       </c>
       <c r="O6">
-        <v>0.9704913600000001</v>
+        <v>0.9676142000000001</v>
       </c>
       <c r="P6">
-        <v>3.881965440000001</v>
+        <v>3.8704568</v>
       </c>
       <c r="Q6">
-        <v>8.57196544</v>
+        <v>8.560456800000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1239157910909727</v>
+        <v>0.1245789132564308</v>
       </c>
       <c r="T6">
-        <v>0.8553999302283462</v>
+        <v>0.8626613897379245</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>85.3271976532414</v>
+        <v>68.26175812259311</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1203619675936093</v>
+        <v>0.1201551757398849</v>
       </c>
       <c r="C7">
-        <v>29.07494405017006</v>
+        <v>28.87265330609404</v>
       </c>
       <c r="D7">
-        <v>30.09894405017006</v>
+        <v>30.18265330609404</v>
       </c>
       <c r="E7">
-        <v>-11.27</v>
+        <v>-10.984</v>
       </c>
       <c r="F7">
-        <v>1.43</v>
+        <v>1.716</v>
       </c>
       <c r="G7">
         <v>0.406</v>
@@ -1989,28 +1989,28 @@
         <v>4.91</v>
       </c>
       <c r="M7">
-        <v>0.07192900000000001</v>
+        <v>0.08631480000000001</v>
       </c>
       <c r="N7">
-        <v>4.838071</v>
+        <v>4.8236852</v>
       </c>
       <c r="O7">
-        <v>0.9676142000000001</v>
+        <v>0.96473704</v>
       </c>
       <c r="P7">
-        <v>3.8704568</v>
+        <v>3.85894816</v>
       </c>
       <c r="Q7">
-        <v>8.560456800000001</v>
+        <v>8.548948159999998</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1245789132564308</v>
+        <v>0.1252561444041328</v>
       </c>
       <c r="T7">
-        <v>0.8626613897379245</v>
+        <v>0.8700773483860048</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>68.26175812259311</v>
+        <v>56.88479843549425</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1201551757398849</v>
+        <v>0.1199483838861604</v>
       </c>
       <c r="C8">
-        <v>28.87265330609404</v>
+        <v>28.67082947420949</v>
       </c>
       <c r="D8">
-        <v>30.18265330609404</v>
+        <v>30.26682947420949</v>
       </c>
       <c r="E8">
-        <v>-10.984</v>
+        <v>-10.698</v>
       </c>
       <c r="F8">
-        <v>1.716</v>
+        <v>2.002</v>
       </c>
       <c r="G8">
         <v>0.406</v>
@@ -2071,28 +2071,28 @@
         <v>4.91</v>
       </c>
       <c r="M8">
-        <v>0.0863148</v>
+        <v>0.1007006</v>
       </c>
       <c r="N8">
-        <v>4.8236852</v>
+        <v>4.8092994</v>
       </c>
       <c r="O8">
-        <v>0.96473704</v>
+        <v>0.9618598800000001</v>
       </c>
       <c r="P8">
-        <v>3.85894816</v>
+        <v>3.84743952</v>
       </c>
       <c r="Q8">
-        <v>8.548948159999998</v>
+        <v>8.53743952</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1252561444041328</v>
+        <v>0.125947939662538</v>
       </c>
       <c r="T8">
-        <v>0.8700773483860048</v>
+        <v>0.8776527900157641</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>56.88479843549426</v>
+        <v>48.75839865899509</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1199483838861604</v>
+        <v>0.1197415920324359</v>
       </c>
       <c r="C9">
-        <v>28.6708294742095</v>
+        <v>28.46947647194506</v>
       </c>
       <c r="D9">
-        <v>30.2668294742095</v>
+        <v>30.35147647194506</v>
       </c>
       <c r="E9">
-        <v>-10.698</v>
+        <v>-10.412</v>
       </c>
       <c r="F9">
-        <v>2.002</v>
+        <v>2.288</v>
       </c>
       <c r="G9">
         <v>0.406</v>
@@ -2153,28 +2153,28 @@
         <v>4.91</v>
       </c>
       <c r="M9">
-        <v>0.1007006</v>
+        <v>0.1150864</v>
       </c>
       <c r="N9">
-        <v>4.8092994</v>
+        <v>4.7949136</v>
       </c>
       <c r="O9">
-        <v>0.9618598800000001</v>
+        <v>0.9589827200000001</v>
       </c>
       <c r="P9">
-        <v>3.84743952</v>
+        <v>3.83593088</v>
       </c>
       <c r="Q9">
-        <v>8.53743952</v>
+        <v>8.525930880000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.125947939662538</v>
+        <v>0.1266547739482999</v>
       </c>
       <c r="T9">
-        <v>0.8776527900157641</v>
+        <v>0.8853929151592138</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>48.75839865899508</v>
+        <v>42.66359882662069</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1197415920324359</v>
+        <v>0.1195348001787115</v>
       </c>
       <c r="C10">
-        <v>28.46947647194506</v>
+        <v>28.2685982606757</v>
       </c>
       <c r="D10">
-        <v>30.35147647194506</v>
+        <v>30.43659826067569</v>
       </c>
       <c r="E10">
-        <v>-10.412</v>
+        <v>-10.126</v>
       </c>
       <c r="F10">
-        <v>2.288</v>
+        <v>2.574</v>
       </c>
       <c r="G10">
         <v>0.406</v>
@@ -2235,28 +2235,28 @@
         <v>4.91</v>
       </c>
       <c r="M10">
-        <v>0.1150864</v>
+        <v>0.1294722</v>
       </c>
       <c r="N10">
-        <v>4.7949136</v>
+        <v>4.7805278</v>
       </c>
       <c r="O10">
-        <v>0.9589827200000001</v>
+        <v>0.95610556</v>
       </c>
       <c r="P10">
-        <v>3.83593088</v>
+        <v>3.82442224</v>
       </c>
       <c r="Q10">
-        <v>8.525930880000001</v>
+        <v>8.514422239999998</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1266547739482999</v>
+        <v>0.1273771430535291</v>
       </c>
       <c r="T10">
-        <v>0.8853929151592138</v>
+        <v>0.8933031529431789</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>42.66359882662069</v>
+        <v>37.92319895699617</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1195348001787115</v>
+        <v>0.119328008324987</v>
       </c>
       <c r="C11">
-        <v>28.2685982606757</v>
+        <v>28.06819884634059</v>
       </c>
       <c r="D11">
-        <v>30.43659826067569</v>
+        <v>30.52219884634059</v>
       </c>
       <c r="E11">
-        <v>-10.126</v>
+        <v>-9.84</v>
       </c>
       <c r="F11">
-        <v>2.574</v>
+        <v>2.86</v>
       </c>
       <c r="G11">
         <v>0.406</v>
@@ -2317,28 +2317,28 @@
         <v>4.91</v>
       </c>
       <c r="M11">
-        <v>0.1294722</v>
+        <v>0.143858</v>
       </c>
       <c r="N11">
-        <v>4.7805278</v>
+        <v>4.766142</v>
       </c>
       <c r="O11">
-        <v>0.95610556</v>
+        <v>0.9532284000000001</v>
       </c>
       <c r="P11">
-        <v>3.82442224</v>
+        <v>3.8129136</v>
       </c>
       <c r="Q11">
-        <v>8.514422239999998</v>
+        <v>8.502913599999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1273771430535291</v>
+        <v>0.1281155648055411</v>
       </c>
       <c r="T11">
-        <v>0.8933031529431789</v>
+        <v>0.9013891737890098</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>37.92319895699617</v>
+        <v>34.13087906129656</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.119328008324987</v>
+        <v>0.1191212164712625</v>
       </c>
       <c r="C12">
-        <v>28.06819884634059</v>
+        <v>27.8682822800716</v>
       </c>
       <c r="D12">
-        <v>30.52219884634059</v>
+        <v>30.60828228007161</v>
       </c>
       <c r="E12">
-        <v>-9.84</v>
+        <v>-9.553999999999998</v>
       </c>
       <c r="F12">
-        <v>2.86</v>
+        <v>3.146</v>
       </c>
       <c r="G12">
         <v>0.406</v>
@@ -2399,28 +2399,28 @@
         <v>4.91</v>
       </c>
       <c r="M12">
-        <v>0.143858</v>
+        <v>0.1582438</v>
       </c>
       <c r="N12">
-        <v>4.766142</v>
+        <v>4.7517562</v>
       </c>
       <c r="O12">
-        <v>0.9532284000000001</v>
+        <v>0.95035124</v>
       </c>
       <c r="P12">
-        <v>3.8129136</v>
+        <v>3.80140496</v>
       </c>
       <c r="Q12">
-        <v>8.502913599999999</v>
+        <v>8.491404960000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1281155648055411</v>
+        <v>0.1288705803047893</v>
       </c>
       <c r="T12">
-        <v>0.90138917378901</v>
+        <v>0.909656902968455</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>34.13087906129655</v>
+        <v>31.02807187390596</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1191212164712625</v>
+        <v>0.1189144246175381</v>
       </c>
       <c r="C13">
-        <v>27.8682822800716</v>
+        <v>27.6688526588324</v>
       </c>
       <c r="D13">
-        <v>30.60828228007161</v>
+        <v>30.6948526588324</v>
       </c>
       <c r="E13">
-        <v>-9.553999999999998</v>
+        <v>-9.267999999999999</v>
       </c>
       <c r="F13">
-        <v>3.146</v>
+        <v>3.432</v>
       </c>
       <c r="G13">
         <v>0.406</v>
@@ -2481,28 +2481,28 @@
         <v>4.91</v>
       </c>
       <c r="M13">
-        <v>0.1582438</v>
+        <v>0.1726296</v>
       </c>
       <c r="N13">
-        <v>4.7517562</v>
+        <v>4.737370400000001</v>
       </c>
       <c r="O13">
-        <v>0.95035124</v>
+        <v>0.9474740800000001</v>
       </c>
       <c r="P13">
-        <v>3.80140496</v>
+        <v>3.78989632</v>
       </c>
       <c r="Q13">
-        <v>8.491404960000001</v>
+        <v>8.47989632</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1288705803047893</v>
+        <v>0.1296427552472023</v>
       </c>
       <c r="T13">
-        <v>0.909656902968455</v>
+        <v>0.9181125350837968</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>31.02807187390596</v>
+        <v>28.44239921774713</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1189144246175381</v>
+        <v>0.1187076327638136</v>
       </c>
       <c r="C14">
-        <v>27.6688526588324</v>
+        <v>27.46991412606837</v>
       </c>
       <c r="D14">
-        <v>30.6948526588324</v>
+        <v>30.78191412606838</v>
       </c>
       <c r="E14">
-        <v>-9.267999999999999</v>
+        <v>-8.981999999999999</v>
       </c>
       <c r="F14">
-        <v>3.432</v>
+        <v>3.718</v>
       </c>
       <c r="G14">
         <v>0.406</v>
@@ -2563,28 +2563,28 @@
         <v>4.91</v>
       </c>
       <c r="M14">
-        <v>0.1726296</v>
+        <v>0.1870154</v>
       </c>
       <c r="N14">
-        <v>4.737370400000001</v>
+        <v>4.7229846</v>
       </c>
       <c r="O14">
-        <v>0.9474740800000001</v>
+        <v>0.9445969200000001</v>
       </c>
       <c r="P14">
-        <v>3.78989632</v>
+        <v>3.77838768</v>
       </c>
       <c r="Q14">
-        <v>8.47989632</v>
+        <v>8.468387679999999</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1296427552472023</v>
+        <v>0.1304326813377168</v>
       </c>
       <c r="T14">
-        <v>0.9181125350837968</v>
+        <v>0.9267625495466174</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>28.44239921774713</v>
+        <v>26.25452235484351</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1187076327638136</v>
+        <v>0.1185008409100891</v>
       </c>
       <c r="C15">
-        <v>27.46991412606837</v>
+        <v>27.27147087236776</v>
       </c>
       <c r="D15">
-        <v>30.78191412606838</v>
+        <v>30.86947087236776</v>
       </c>
       <c r="E15">
-        <v>-8.981999999999999</v>
+        <v>-8.695999999999998</v>
       </c>
       <c r="F15">
-        <v>3.718</v>
+        <v>4.004</v>
       </c>
       <c r="G15">
         <v>0.406</v>
@@ -2645,28 +2645,28 @@
         <v>4.91</v>
       </c>
       <c r="M15">
-        <v>0.1870154</v>
+        <v>0.2014012</v>
       </c>
       <c r="N15">
-        <v>4.7229846</v>
+        <v>4.7085988</v>
       </c>
       <c r="O15">
-        <v>0.9445969200000001</v>
+        <v>0.94171976</v>
       </c>
       <c r="P15">
-        <v>3.77838768</v>
+        <v>3.76687904</v>
       </c>
       <c r="Q15">
-        <v>8.468387679999999</v>
+        <v>8.45687904</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1304326813377168</v>
+        <v>0.1312409778024292</v>
       </c>
       <c r="T15">
-        <v>0.9267625495466174</v>
+        <v>0.9356137271364806</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>26.25452235484351</v>
+        <v>24.37919932949754</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1185008409100891</v>
+        <v>0.1182940490563647</v>
       </c>
       <c r="C16">
-        <v>27.27147087236776</v>
+        <v>27.07352713613401</v>
       </c>
       <c r="D16">
-        <v>30.86947087236776</v>
+        <v>30.95752713613401</v>
       </c>
       <c r="E16">
-        <v>-8.695999999999998</v>
+        <v>-8.409999999999998</v>
       </c>
       <c r="F16">
-        <v>4.004</v>
+        <v>4.290000000000001</v>
       </c>
       <c r="G16">
         <v>0.406</v>
@@ -2727,28 +2727,28 @@
         <v>4.91</v>
       </c>
       <c r="M16">
-        <v>0.2014012</v>
+        <v>0.215787</v>
       </c>
       <c r="N16">
-        <v>4.7085988</v>
+        <v>4.694213</v>
       </c>
       <c r="O16">
-        <v>0.94171976</v>
+        <v>0.9388426000000001</v>
       </c>
       <c r="P16">
-        <v>3.76687904</v>
+        <v>3.7553704</v>
       </c>
       <c r="Q16">
-        <v>8.45687904</v>
+        <v>8.4453704</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1312409778024292</v>
+        <v>0.1320682930074878</v>
       </c>
       <c r="T16">
-        <v>0.9356137271364806</v>
+        <v>0.9446731677284581</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>24.37919932949754</v>
+        <v>22.7539193741977</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1182940490563647</v>
+        <v>0.1180872572026402</v>
       </c>
       <c r="C17">
-        <v>27.07352713613401</v>
+        <v>26.87608720426968</v>
       </c>
       <c r="D17">
-        <v>30.95752713613401</v>
+        <v>31.04608720426968</v>
       </c>
       <c r="E17">
-        <v>-8.41</v>
+        <v>-8.123999999999999</v>
       </c>
       <c r="F17">
-        <v>4.29</v>
+        <v>4.576000000000001</v>
       </c>
       <c r="G17">
         <v>0.406</v>
@@ -2809,28 +2809,28 @@
         <v>4.91</v>
       </c>
       <c r="M17">
-        <v>0.215787</v>
+        <v>0.2301728</v>
       </c>
       <c r="N17">
-        <v>4.694213</v>
+        <v>4.6798272</v>
       </c>
       <c r="O17">
-        <v>0.9388426000000001</v>
+        <v>0.93596544</v>
       </c>
       <c r="P17">
-        <v>3.7553704</v>
+        <v>3.74386176</v>
       </c>
       <c r="Q17">
-        <v>8.4453704</v>
+        <v>8.433861759999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1320682930074878</v>
+        <v>0.1329153061936193</v>
       </c>
       <c r="T17">
-        <v>0.9446731677284581</v>
+        <v>0.9539483092869112</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>22.75391937419771</v>
+        <v>21.33179941331035</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1180872572026402</v>
+        <v>0.1178804653489157</v>
       </c>
       <c r="C18">
-        <v>26.87608720426968</v>
+        <v>26.67915541287218</v>
       </c>
       <c r="D18">
-        <v>31.04608720426968</v>
+        <v>31.13515541287218</v>
       </c>
       <c r="E18">
-        <v>-8.123999999999999</v>
+        <v>-7.837999999999998</v>
       </c>
       <c r="F18">
-        <v>4.576000000000001</v>
+        <v>4.862000000000001</v>
       </c>
       <c r="G18">
         <v>0.406</v>
@@ -2891,28 +2891,28 @@
         <v>4.91</v>
       </c>
       <c r="M18">
-        <v>0.2301728</v>
+        <v>0.2445586</v>
       </c>
       <c r="N18">
-        <v>4.6798272</v>
+        <v>4.6654414</v>
       </c>
       <c r="O18">
-        <v>0.93596544</v>
+        <v>0.93308828</v>
       </c>
       <c r="P18">
-        <v>3.74386176</v>
+        <v>3.73235312</v>
       </c>
       <c r="Q18">
-        <v>8.433861759999999</v>
+        <v>8.42235312</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1329153061936193</v>
+        <v>0.1337827293360431</v>
       </c>
       <c r="T18">
-        <v>0.9539483092869112</v>
+        <v>0.9634469482323151</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>21.33179941331035</v>
+        <v>20.07698768311562</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1178804653489157</v>
+        <v>0.1176736734951913</v>
       </c>
       <c r="C19">
-        <v>26.67915541287218</v>
+        <v>26.48273614794143</v>
       </c>
       <c r="D19">
-        <v>31.13515541287218</v>
+        <v>31.22473614794143</v>
       </c>
       <c r="E19">
-        <v>-7.837999999999998</v>
+        <v>-7.551999999999999</v>
       </c>
       <c r="F19">
-        <v>4.862000000000001</v>
+        <v>5.148000000000001</v>
       </c>
       <c r="G19">
         <v>0.406</v>
@@ -2973,28 +2973,28 @@
         <v>4.91</v>
       </c>
       <c r="M19">
-        <v>0.2445586</v>
+        <v>0.2589444</v>
       </c>
       <c r="N19">
-        <v>4.6654414</v>
+        <v>4.6510556</v>
       </c>
       <c r="O19">
-        <v>0.93308828</v>
+        <v>0.9302111200000001</v>
       </c>
       <c r="P19">
-        <v>3.73235312</v>
+        <v>3.72084448</v>
       </c>
       <c r="Q19">
-        <v>8.42235312</v>
+        <v>8.41084448</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1337827293360431</v>
+        <v>0.1346713091404772</v>
       </c>
       <c r="T19">
-        <v>0.9634469482323151</v>
+        <v>0.9731772612983388</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>20.07698768311562</v>
+        <v>18.96159947849809</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1176736734951913</v>
+        <v>0.1174668816414668</v>
       </c>
       <c r="C20">
-        <v>26.48273614794142</v>
+        <v>26.28683384609987</v>
       </c>
       <c r="D20">
-        <v>31.22473614794142</v>
+        <v>31.31483384609987</v>
       </c>
       <c r="E20">
-        <v>-7.552</v>
+        <v>-7.265999999999999</v>
       </c>
       <c r="F20">
-        <v>5.148</v>
+        <v>5.434</v>
       </c>
       <c r="G20">
         <v>0.406</v>
@@ -3055,28 +3055,28 @@
         <v>4.91</v>
       </c>
       <c r="M20">
-        <v>0.2589444</v>
+        <v>0.2733302</v>
       </c>
       <c r="N20">
-        <v>4.6510556</v>
+        <v>4.6366698</v>
       </c>
       <c r="O20">
-        <v>0.9302111200000001</v>
+        <v>0.92733396</v>
       </c>
       <c r="P20">
-        <v>3.72084448</v>
+        <v>3.70933584</v>
       </c>
       <c r="Q20">
-        <v>8.41084448</v>
+        <v>8.399335839999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1346713091404772</v>
+        <v>0.1355818291869961</v>
       </c>
       <c r="T20">
-        <v>0.9731772612983386</v>
+        <v>0.9831478290079678</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>18.96159947849809</v>
+        <v>17.96362055857714</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1174668816414668</v>
+        <v>0.1172600897877424</v>
       </c>
       <c r="C21">
-        <v>26.28683384609987</v>
+        <v>26.09145299532489</v>
       </c>
       <c r="D21">
-        <v>31.31483384609987</v>
+        <v>31.4054529953249</v>
       </c>
       <c r="E21">
-        <v>-7.265999999999999</v>
+        <v>-6.979999999999999</v>
       </c>
       <c r="F21">
-        <v>5.434</v>
+        <v>5.720000000000001</v>
       </c>
       <c r="G21">
         <v>0.406</v>
@@ -3137,28 +3137,28 @@
         <v>4.91</v>
       </c>
       <c r="M21">
-        <v>0.2733302</v>
+        <v>0.287716</v>
       </c>
       <c r="N21">
-        <v>4.6366698</v>
+        <v>4.622284000000001</v>
       </c>
       <c r="O21">
-        <v>0.92733396</v>
+        <v>0.9244568000000002</v>
       </c>
       <c r="P21">
-        <v>3.70933584</v>
+        <v>3.6978272</v>
       </c>
       <c r="Q21">
-        <v>8.399335839999999</v>
+        <v>8.3878272</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1355818291869961</v>
+        <v>0.1365151122346779</v>
       </c>
       <c r="T21">
-        <v>0.9831478290079678</v>
+        <v>0.9933676609103373</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>17.96362055857714</v>
+        <v>17.06543953064828</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1172600897877424</v>
+        <v>0.1170532979340179</v>
       </c>
       <c r="C22">
-        <v>26.09145299532489</v>
+        <v>25.89659813569402</v>
       </c>
       <c r="D22">
-        <v>31.4054529953249</v>
+        <v>31.49659813569403</v>
       </c>
       <c r="E22">
-        <v>-6.979999999999999</v>
+        <v>-6.693999999999998</v>
       </c>
       <c r="F22">
-        <v>5.720000000000001</v>
+        <v>6.006000000000001</v>
       </c>
       <c r="G22">
         <v>0.406</v>
@@ -3219,28 +3219,28 @@
         <v>4.91</v>
       </c>
       <c r="M22">
-        <v>0.287716</v>
+        <v>0.3021018</v>
       </c>
       <c r="N22">
-        <v>4.622284000000001</v>
+        <v>4.6078982</v>
       </c>
       <c r="O22">
-        <v>0.9244568000000002</v>
+        <v>0.92157964</v>
       </c>
       <c r="P22">
-        <v>3.6978272</v>
+        <v>3.68631856</v>
       </c>
       <c r="Q22">
-        <v>8.3878272</v>
+        <v>8.37631856</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1365151122346779</v>
+        <v>0.1374720227012885</v>
       </c>
       <c r="T22">
-        <v>0.9933676609103373</v>
+        <v>1.003846222734286</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>17.06543953064828</v>
+        <v>16.25279955299836</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1170532979340179</v>
+        <v>0.1168465060802934</v>
       </c>
       <c r="C23">
-        <v>25.89659813569402</v>
+        <v>25.70227386014322</v>
       </c>
       <c r="D23">
-        <v>31.49659813569403</v>
+        <v>31.58827386014322</v>
       </c>
       <c r="E23">
-        <v>-6.693999999999999</v>
+        <v>-6.407999999999999</v>
       </c>
       <c r="F23">
-        <v>6.006</v>
+        <v>6.292000000000001</v>
       </c>
       <c r="G23">
         <v>0.406</v>
@@ -3301,28 +3301,28 @@
         <v>4.91</v>
       </c>
       <c r="M23">
-        <v>0.3021018</v>
+        <v>0.3164876</v>
       </c>
       <c r="N23">
-        <v>4.6078982</v>
+        <v>4.5935124</v>
       </c>
       <c r="O23">
-        <v>0.92157964</v>
+        <v>0.91870248</v>
       </c>
       <c r="P23">
-        <v>3.68631856</v>
+        <v>3.67480992</v>
       </c>
       <c r="Q23">
-        <v>8.37631856</v>
+        <v>8.364809919999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1374720227012885</v>
+        <v>0.1384534693337095</v>
       </c>
       <c r="T23">
-        <v>1.003846222734286</v>
+        <v>1.014593465630644</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>16.25279955299836</v>
+        <v>15.51403593695298</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1168465060802934</v>
+        <v>0.116639714226569</v>
       </c>
       <c r="C24">
-        <v>25.70227386014322</v>
+        <v>25.5084848152383</v>
       </c>
       <c r="D24">
-        <v>31.58827386014322</v>
+        <v>31.6804848152383</v>
       </c>
       <c r="E24">
-        <v>-6.407999999999999</v>
+        <v>-6.121999999999999</v>
       </c>
       <c r="F24">
-        <v>6.292000000000001</v>
+        <v>6.578</v>
       </c>
       <c r="G24">
         <v>0.406</v>
@@ -3383,28 +3383,28 @@
         <v>4.91</v>
       </c>
       <c r="M24">
-        <v>0.3164876</v>
+        <v>0.3308734</v>
       </c>
       <c r="N24">
-        <v>4.5935124</v>
+        <v>4.5791266</v>
       </c>
       <c r="O24">
-        <v>0.91870248</v>
+        <v>0.9158253200000002</v>
       </c>
       <c r="P24">
-        <v>3.67480992</v>
+        <v>3.66330128</v>
       </c>
       <c r="Q24">
-        <v>8.364809919999999</v>
+        <v>8.35330128</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1384534693337095</v>
+        <v>0.1394604080864532</v>
       </c>
       <c r="T24">
-        <v>1.014593465630644</v>
+        <v>1.025619857693141</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>15.51403593695298</v>
+        <v>14.83951263534633</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.116639714226569</v>
+        <v>0.1164329223728445</v>
       </c>
       <c r="C25">
-        <v>25.5084848152383</v>
+        <v>25.3152357019601</v>
       </c>
       <c r="D25">
-        <v>31.6804848152383</v>
+        <v>31.7732357019601</v>
       </c>
       <c r="E25">
-        <v>-6.121999999999999</v>
+        <v>-5.835999999999999</v>
       </c>
       <c r="F25">
-        <v>6.578</v>
+        <v>6.864000000000001</v>
       </c>
       <c r="G25">
         <v>0.406</v>
@@ -3465,28 +3465,28 @@
         <v>4.91</v>
       </c>
       <c r="M25">
-        <v>0.3308734</v>
+        <v>0.3452592</v>
       </c>
       <c r="N25">
-        <v>4.5791266</v>
+        <v>4.5647408</v>
       </c>
       <c r="O25">
-        <v>0.9158253200000002</v>
+        <v>0.91294816</v>
       </c>
       <c r="P25">
-        <v>3.66330128</v>
+        <v>3.65179264</v>
       </c>
       <c r="Q25">
-        <v>8.35330128</v>
+        <v>8.34179264</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1394604080864532</v>
+        <v>0.140493845227427</v>
       </c>
       <c r="T25">
-        <v>1.025619857693141</v>
+        <v>1.036936417967808</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>14.83951263534633</v>
+        <v>14.22119960887356</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1164329223728445</v>
+        <v>0.11622613051912</v>
       </c>
       <c r="C26">
-        <v>25.3152357019601</v>
+        <v>25.12253127650327</v>
       </c>
       <c r="D26">
-        <v>31.7732357019601</v>
+        <v>31.86653127650326</v>
       </c>
       <c r="E26">
-        <v>-5.835999999999999</v>
+        <v>-5.549999999999999</v>
       </c>
       <c r="F26">
-        <v>6.864</v>
+        <v>7.15</v>
       </c>
       <c r="G26">
         <v>0.406</v>
@@ -3547,28 +3547,28 @@
         <v>4.91</v>
       </c>
       <c r="M26">
-        <v>0.3452592</v>
+        <v>0.359645</v>
       </c>
       <c r="N26">
-        <v>4.5647408</v>
+        <v>4.550355</v>
       </c>
       <c r="O26">
-        <v>0.91294816</v>
+        <v>0.910071</v>
       </c>
       <c r="P26">
-        <v>3.65179264</v>
+        <v>3.640284</v>
       </c>
       <c r="Q26">
-        <v>8.34179264</v>
+        <v>8.330283999999999</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.140493845227427</v>
+        <v>0.14155484069216</v>
       </c>
       <c r="T26">
-        <v>1.036936417967808</v>
+        <v>1.048554753183134</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>14.22119960887357</v>
+        <v>13.65235162451862</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.11622613051912</v>
+        <v>0.1160193386653956</v>
       </c>
       <c r="C27">
-        <v>25.12253127650327</v>
+        <v>24.9303763510893</v>
       </c>
       <c r="D27">
-        <v>31.86653127650326</v>
+        <v>31.9603763510893</v>
       </c>
       <c r="E27">
-        <v>-5.549999999999999</v>
+        <v>-5.263999999999998</v>
       </c>
       <c r="F27">
-        <v>7.15</v>
+        <v>7.436000000000001</v>
       </c>
       <c r="G27">
         <v>0.406</v>
@@ -3629,28 +3629,28 @@
         <v>4.91</v>
       </c>
       <c r="M27">
-        <v>0.359645</v>
+        <v>0.3740308</v>
       </c>
       <c r="N27">
-        <v>4.550355</v>
+        <v>4.5359692</v>
       </c>
       <c r="O27">
-        <v>0.910071</v>
+        <v>0.9071938400000001</v>
       </c>
       <c r="P27">
-        <v>3.640284</v>
+        <v>3.62877536</v>
       </c>
       <c r="Q27">
-        <v>8.330283999999999</v>
+        <v>8.31877536</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.14155484069216</v>
+        <v>0.142644511709994</v>
       </c>
       <c r="T27">
-        <v>1.048554753183134</v>
+        <v>1.060487097458333</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>13.65235162451862</v>
+        <v>13.12726117742175</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1160193386653956</v>
+        <v>0.1161365468116711</v>
       </c>
       <c r="C28">
-        <v>24.9303763510893</v>
+        <v>24.59111788680315</v>
       </c>
       <c r="D28">
-        <v>31.9603763510893</v>
+        <v>31.90711788680315</v>
       </c>
       <c r="E28">
-        <v>-5.263999999999998</v>
+        <v>-4.977999999999998</v>
       </c>
       <c r="F28">
-        <v>7.436000000000001</v>
+        <v>7.722000000000001</v>
       </c>
       <c r="G28">
         <v>0.406</v>
@@ -3711,45 +3711,45 @@
         <v>4.91</v>
       </c>
       <c r="M28">
-        <v>0.3740308</v>
+        <v>0.3999996000000001</v>
       </c>
       <c r="N28">
-        <v>4.5359692</v>
+        <v>4.5100004</v>
       </c>
       <c r="O28">
-        <v>0.9071938400000001</v>
+        <v>0.9020000800000001</v>
       </c>
       <c r="P28">
-        <v>3.62877536</v>
+        <v>3.60800032</v>
       </c>
       <c r="Q28">
-        <v>8.31877536</v>
+        <v>8.29800032</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.142644511709994</v>
+        <v>0.1437640367283166</v>
       </c>
       <c r="T28">
-        <v>1.060487097458333</v>
+        <v>1.072746355275319</v>
       </c>
       <c r="U28">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V28">
         <v>0.2</v>
       </c>
       <c r="W28">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y28">
-        <v>13.12726117742175</v>
+        <v>12.27501227501227</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1161365468116711</v>
+        <v>0.1159417549579466</v>
       </c>
       <c r="C29">
-        <v>24.59111788680315</v>
+        <v>24.39372768340579</v>
       </c>
       <c r="D29">
-        <v>31.90711788680315</v>
+        <v>31.9957276834058</v>
       </c>
       <c r="E29">
-        <v>-4.977999999999998</v>
+        <v>-4.691999999999998</v>
       </c>
       <c r="F29">
-        <v>7.722000000000001</v>
+        <v>8.008000000000001</v>
       </c>
       <c r="G29">
         <v>0.406</v>
@@ -3793,28 +3793,28 @@
         <v>4.91</v>
       </c>
       <c r="M29">
-        <v>0.3999996000000001</v>
+        <v>0.4148144</v>
       </c>
       <c r="N29">
-        <v>4.5100004</v>
+        <v>4.4951856</v>
       </c>
       <c r="O29">
-        <v>0.9020000800000001</v>
+        <v>0.89903712</v>
       </c>
       <c r="P29">
-        <v>3.60800032</v>
+        <v>3.59614848</v>
       </c>
       <c r="Q29">
-        <v>8.29800032</v>
+        <v>8.28614848</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1437640367283166</v>
+        <v>0.1449146596638148</v>
       </c>
       <c r="T29">
-        <v>1.072746355275319</v>
+        <v>1.085346148031665</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>12.27501227501227</v>
+        <v>11.83661897947612</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1159417549579466</v>
+        <v>0.1157469631042222</v>
       </c>
       <c r="C30">
-        <v>24.39372768340579</v>
+        <v>24.19683101012816</v>
       </c>
       <c r="D30">
-        <v>31.9957276834058</v>
+        <v>32.08483101012817</v>
       </c>
       <c r="E30">
-        <v>-4.691999999999998</v>
+        <v>-4.405999999999997</v>
       </c>
       <c r="F30">
-        <v>8.008000000000001</v>
+        <v>8.294000000000002</v>
       </c>
       <c r="G30">
         <v>0.406</v>
@@ -3875,28 +3875,28 @@
         <v>4.91</v>
       </c>
       <c r="M30">
-        <v>0.4148144</v>
+        <v>0.4296292000000001</v>
       </c>
       <c r="N30">
-        <v>4.4951856</v>
+        <v>4.4803708</v>
       </c>
       <c r="O30">
-        <v>0.89903712</v>
+        <v>0.8960741600000001</v>
       </c>
       <c r="P30">
-        <v>3.59614848</v>
+        <v>3.58429664</v>
       </c>
       <c r="Q30">
-        <v>8.28614848</v>
+        <v>8.274296639999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1449146596638148</v>
+        <v>0.146097694512989</v>
       </c>
       <c r="T30">
-        <v>1.085346148031665</v>
+        <v>1.098300864527627</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.83661897947612</v>
+        <v>11.42845970432177</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1157469631042222</v>
+        <v>0.1155521712504977</v>
       </c>
       <c r="C31">
-        <v>24.19683101012817</v>
+        <v>24.00043200170813</v>
       </c>
       <c r="D31">
-        <v>32.08483101012817</v>
+        <v>32.17443200170813</v>
       </c>
       <c r="E31">
-        <v>-4.405999999999999</v>
+        <v>-4.119999999999999</v>
       </c>
       <c r="F31">
-        <v>8.294</v>
+        <v>8.58</v>
       </c>
       <c r="G31">
         <v>0.406</v>
@@ -3957,28 +3957,28 @@
         <v>4.91</v>
       </c>
       <c r="M31">
-        <v>0.4296292</v>
+        <v>0.444444</v>
       </c>
       <c r="N31">
-        <v>4.4803708</v>
+        <v>4.465556</v>
       </c>
       <c r="O31">
-        <v>0.8960741600000001</v>
+        <v>0.8931112000000001</v>
       </c>
       <c r="P31">
-        <v>3.58429664</v>
+        <v>3.5724448</v>
       </c>
       <c r="Q31">
-        <v>8.274296639999999</v>
+        <v>8.262444800000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.146097694512989</v>
+        <v>0.1473145303578539</v>
       </c>
       <c r="T31">
-        <v>1.098300864527627</v>
+        <v>1.111625715780616</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>11.42845970432177</v>
+        <v>11.04751104751105</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1155521712504977</v>
+        <v>0.1153573793967732</v>
       </c>
       <c r="C32">
-        <v>24.00043200170813</v>
+        <v>23.80453483919995</v>
       </c>
       <c r="D32">
-        <v>32.17443200170813</v>
+        <v>32.26453483919995</v>
       </c>
       <c r="E32">
-        <v>-4.119999999999999</v>
+        <v>-3.834</v>
       </c>
       <c r="F32">
-        <v>8.58</v>
+        <v>8.866</v>
       </c>
       <c r="G32">
         <v>0.406</v>
@@ -4039,28 +4039,28 @@
         <v>4.91</v>
       </c>
       <c r="M32">
-        <v>0.444444</v>
+        <v>0.4592588</v>
       </c>
       <c r="N32">
-        <v>4.465556</v>
+        <v>4.4507412</v>
       </c>
       <c r="O32">
-        <v>0.8931112000000001</v>
+        <v>0.8901482400000001</v>
       </c>
       <c r="P32">
-        <v>3.5724448</v>
+        <v>3.56059296</v>
       </c>
       <c r="Q32">
-        <v>8.262444800000001</v>
+        <v>8.250592959999999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1473145303578539</v>
+        <v>0.1485666368069178</v>
       </c>
       <c r="T32">
-        <v>1.111625715780616</v>
+        <v>1.125336794606155</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>11.04751104751105</v>
+        <v>10.69113972339779</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1153573793967732</v>
+        <v>0.1151625875430488</v>
       </c>
       <c r="C33">
-        <v>23.80453483919995</v>
+        <v>23.60914375062477</v>
       </c>
       <c r="D33">
-        <v>32.26453483919995</v>
+        <v>32.35514375062477</v>
       </c>
       <c r="E33">
-        <v>-3.834</v>
+        <v>-3.547999999999998</v>
       </c>
       <c r="F33">
-        <v>8.866</v>
+        <v>9.152000000000001</v>
       </c>
       <c r="G33">
         <v>0.406</v>
@@ -4121,28 +4121,28 @@
         <v>4.91</v>
       </c>
       <c r="M33">
-        <v>0.4592588</v>
+        <v>0.4740736</v>
       </c>
       <c r="N33">
-        <v>4.4507412</v>
+        <v>4.4359264</v>
       </c>
       <c r="O33">
-        <v>0.8901482400000001</v>
+        <v>0.8871852800000002</v>
       </c>
       <c r="P33">
-        <v>3.56059296</v>
+        <v>3.54874112</v>
       </c>
       <c r="Q33">
-        <v>8.250592959999999</v>
+        <v>8.23874112</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1485666368069178</v>
+        <v>0.1498555699162482</v>
       </c>
       <c r="T33">
-        <v>1.125336794606155</v>
+        <v>1.139451140455975</v>
       </c>
       <c r="U33">
         <v>0.0518</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>10.69113972339779</v>
+        <v>10.35704160704161</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1151625875430488</v>
+        <v>0.1149677956893243</v>
       </c>
       <c r="C34">
-        <v>23.60914375062477</v>
+        <v>23.41426301163194</v>
       </c>
       <c r="D34">
-        <v>32.35514375062477</v>
+        <v>32.44626301163194</v>
       </c>
       <c r="E34">
-        <v>-3.547999999999998</v>
+        <v>-3.261999999999999</v>
       </c>
       <c r="F34">
-        <v>9.152000000000001</v>
+        <v>9.438000000000001</v>
       </c>
       <c r="G34">
         <v>0.406</v>
@@ -4203,28 +4203,28 @@
         <v>4.91</v>
       </c>
       <c r="M34">
-        <v>0.4740736</v>
+        <v>0.4888884</v>
       </c>
       <c r="N34">
-        <v>4.4359264</v>
+        <v>4.4211116</v>
       </c>
       <c r="O34">
-        <v>0.8871852800000002</v>
+        <v>0.88422232</v>
       </c>
       <c r="P34">
-        <v>3.54874112</v>
+        <v>3.53688928</v>
       </c>
       <c r="Q34">
-        <v>8.23874112</v>
+        <v>8.226889279999998</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1498555699162482</v>
+        <v>0.1511829786407826</v>
       </c>
       <c r="T34">
-        <v>1.139451140455975</v>
+        <v>1.153986810062506</v>
       </c>
       <c r="U34">
         <v>0.0518</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>10.35704160704161</v>
+        <v>10.04319186137368</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1149677956893243</v>
+        <v>0.1152354038355999</v>
       </c>
       <c r="C35">
-        <v>23.41426301163194</v>
+        <v>23.00321319815826</v>
       </c>
       <c r="D35">
-        <v>32.44626301163194</v>
+        <v>32.32121319815826</v>
       </c>
       <c r="E35">
-        <v>-3.261999999999999</v>
+        <v>-2.975999999999997</v>
       </c>
       <c r="F35">
-        <v>9.438000000000001</v>
+        <v>9.724000000000002</v>
       </c>
       <c r="G35">
         <v>0.406</v>
@@ -4285,45 +4285,45 @@
         <v>4.91</v>
       </c>
       <c r="M35">
-        <v>0.4888884</v>
+        <v>0.5202340000000001</v>
       </c>
       <c r="N35">
-        <v>4.4211116</v>
+        <v>4.389766</v>
       </c>
       <c r="O35">
-        <v>0.88422232</v>
+        <v>0.8779532</v>
       </c>
       <c r="P35">
-        <v>3.53688928</v>
+        <v>3.5118128</v>
       </c>
       <c r="Q35">
-        <v>8.226889279999998</v>
+        <v>8.201812799999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1511829786407826</v>
+        <v>0.152550611872121</v>
       </c>
       <c r="T35">
-        <v>1.153986810062506</v>
+        <v>1.168962954505599</v>
       </c>
       <c r="U35">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V35">
         <v>0.2</v>
       </c>
       <c r="W35">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y35">
-        <v>10.04319186137368</v>
+        <v>9.438060565053416</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1152354038355999</v>
+        <v>0.1150542119818754</v>
       </c>
       <c r="C36">
-        <v>23.00321319815826</v>
+        <v>22.80177614915293</v>
       </c>
       <c r="D36">
-        <v>32.32121319815826</v>
+        <v>32.40577614915293</v>
       </c>
       <c r="E36">
-        <v>-2.975999999999997</v>
+        <v>-2.689999999999998</v>
       </c>
       <c r="F36">
-        <v>9.724000000000002</v>
+        <v>10.01</v>
       </c>
       <c r="G36">
         <v>0.406</v>
@@ -4367,28 +4367,28 @@
         <v>4.91</v>
       </c>
       <c r="M36">
-        <v>0.5202340000000001</v>
+        <v>0.5355350000000001</v>
       </c>
       <c r="N36">
-        <v>4.389766</v>
+        <v>4.374465</v>
       </c>
       <c r="O36">
-        <v>0.8779532</v>
+        <v>0.874893</v>
       </c>
       <c r="P36">
-        <v>3.5118128</v>
+        <v>3.499572</v>
       </c>
       <c r="Q36">
-        <v>8.201812799999999</v>
+        <v>8.189571999999998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.152550611872121</v>
+        <v>0.1539603261259622</v>
       </c>
       <c r="T36">
-        <v>1.168962954505599</v>
+        <v>1.184399903393095</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>9.438060565053416</v>
+        <v>9.168401691766176</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1150542119818754</v>
+        <v>0.1148730201281509</v>
       </c>
       <c r="C37">
-        <v>22.80177614915293</v>
+        <v>22.60078275000738</v>
       </c>
       <c r="D37">
-        <v>32.40577614915293</v>
+        <v>32.49078275000738</v>
       </c>
       <c r="E37">
-        <v>-2.689999999999998</v>
+        <v>-2.403999999999998</v>
       </c>
       <c r="F37">
-        <v>10.01</v>
+        <v>10.296</v>
       </c>
       <c r="G37">
         <v>0.406</v>
@@ -4449,28 +4449,28 @@
         <v>4.91</v>
       </c>
       <c r="M37">
-        <v>0.5355350000000001</v>
+        <v>0.5508360000000001</v>
       </c>
       <c r="N37">
-        <v>4.374465</v>
+        <v>4.359164</v>
       </c>
       <c r="O37">
-        <v>0.874893</v>
+        <v>0.8718328</v>
       </c>
       <c r="P37">
-        <v>3.499572</v>
+        <v>3.4873312</v>
       </c>
       <c r="Q37">
-        <v>8.189571999999998</v>
+        <v>8.177331199999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1539603261259622</v>
+        <v>0.1554140939502359</v>
       </c>
       <c r="T37">
-        <v>1.184399903393095</v>
+        <v>1.200319256933325</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>9.168401691766176</v>
+        <v>8.913723866994893</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1148730201281509</v>
+        <v>0.1146918282744265</v>
       </c>
       <c r="C38">
-        <v>22.60078275000738</v>
+        <v>22.40023650124158</v>
       </c>
       <c r="D38">
-        <v>32.49078275000738</v>
+        <v>32.57623650124158</v>
       </c>
       <c r="E38">
-        <v>-2.404</v>
+        <v>-2.117999999999999</v>
       </c>
       <c r="F38">
-        <v>10.296</v>
+        <v>10.582</v>
       </c>
       <c r="G38">
         <v>0.406</v>
@@ -4531,28 +4531,28 @@
         <v>4.91</v>
       </c>
       <c r="M38">
-        <v>0.550836</v>
+        <v>0.566137</v>
       </c>
       <c r="N38">
-        <v>4.359164</v>
+        <v>4.343863</v>
       </c>
       <c r="O38">
-        <v>0.8718328</v>
+        <v>0.8687726</v>
       </c>
       <c r="P38">
-        <v>3.4873312</v>
+        <v>3.4750904</v>
       </c>
       <c r="Q38">
-        <v>8.177331199999999</v>
+        <v>8.1650904</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1554140939502358</v>
+        <v>0.1569140131340103</v>
       </c>
       <c r="T38">
-        <v>1.200319256933324</v>
+        <v>1.216743986776419</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.913723866994895</v>
+        <v>8.672812411130167</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1146918282744265</v>
+        <v>0.114510636420702</v>
       </c>
       <c r="C39">
-        <v>22.40023650124158</v>
+        <v>22.20014094029941</v>
       </c>
       <c r="D39">
-        <v>32.57623650124158</v>
+        <v>32.66214094029942</v>
       </c>
       <c r="E39">
-        <v>-2.117999999999999</v>
+        <v>-1.831999999999999</v>
       </c>
       <c r="F39">
-        <v>10.582</v>
+        <v>10.868</v>
       </c>
       <c r="G39">
         <v>0.406</v>
@@ -4613,28 +4613,28 @@
         <v>4.91</v>
       </c>
       <c r="M39">
-        <v>0.566137</v>
+        <v>0.581438</v>
       </c>
       <c r="N39">
-        <v>4.343863</v>
+        <v>4.328562</v>
       </c>
       <c r="O39">
-        <v>0.8687726</v>
+        <v>0.8657124</v>
       </c>
       <c r="P39">
-        <v>3.4750904</v>
+        <v>3.4628496</v>
       </c>
       <c r="Q39">
-        <v>8.1650904</v>
+        <v>8.1528496</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1569140131340103</v>
+        <v>0.1584623168075839</v>
       </c>
       <c r="T39">
-        <v>1.216743986776419</v>
+        <v>1.233698546614451</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.672812411130167</v>
+        <v>8.444580505574111</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.114510636420702</v>
+        <v>0.1143294445669776</v>
       </c>
       <c r="C40">
-        <v>22.20014094029941</v>
+        <v>22.00049964203671</v>
       </c>
       <c r="D40">
-        <v>32.66214094029942</v>
+        <v>32.74849964203671</v>
       </c>
       <c r="E40">
-        <v>-1.831999999999999</v>
+        <v>-1.545999999999998</v>
       </c>
       <c r="F40">
-        <v>10.868</v>
+        <v>11.154</v>
       </c>
       <c r="G40">
         <v>0.406</v>
@@ -4695,28 +4695,28 @@
         <v>4.91</v>
       </c>
       <c r="M40">
-        <v>0.581438</v>
+        <v>0.5967390000000001</v>
       </c>
       <c r="N40">
-        <v>4.328562</v>
+        <v>4.313261</v>
       </c>
       <c r="O40">
-        <v>0.8657124</v>
+        <v>0.8626522</v>
       </c>
       <c r="P40">
-        <v>3.4628496</v>
+        <v>3.4506088</v>
       </c>
       <c r="Q40">
-        <v>8.1528496</v>
+        <v>8.140608799999999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1584623168075839</v>
+        <v>0.1600613845360288</v>
       </c>
       <c r="T40">
-        <v>1.233698546614451</v>
+        <v>1.251208993660288</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>8.444580505574111</v>
+        <v>8.228052800302979</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1143294445669776</v>
+        <v>0.1141482527132531</v>
       </c>
       <c r="C41">
-        <v>22.00049964203671</v>
+        <v>21.80131621921725</v>
       </c>
       <c r="D41">
-        <v>32.74849964203671</v>
+        <v>32.83531621921725</v>
       </c>
       <c r="E41">
-        <v>-1.545999999999998</v>
+        <v>-1.259999999999998</v>
       </c>
       <c r="F41">
-        <v>11.154</v>
+        <v>11.44</v>
       </c>
       <c r="G41">
         <v>0.406</v>
@@ -4777,28 +4777,28 @@
         <v>4.91</v>
       </c>
       <c r="M41">
-        <v>0.5967390000000001</v>
+        <v>0.61204</v>
       </c>
       <c r="N41">
-        <v>4.313261</v>
+        <v>4.29796</v>
       </c>
       <c r="O41">
-        <v>0.8626522</v>
+        <v>0.859592</v>
       </c>
       <c r="P41">
-        <v>3.4506088</v>
+        <v>3.438368</v>
       </c>
       <c r="Q41">
-        <v>8.140608799999999</v>
+        <v>8.128367999999998</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1600613845360288</v>
+        <v>0.1617137545220885</v>
       </c>
       <c r="T41">
-        <v>1.251208993660288</v>
+        <v>1.26930312227432</v>
       </c>
       <c r="U41">
         <v>0.0535</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>8.228052800302979</v>
+        <v>8.022351480295406</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1141482527132531</v>
+        <v>0.1139670608595286</v>
       </c>
       <c r="C42">
-        <v>21.80131621921725</v>
+        <v>21.60259432301652</v>
       </c>
       <c r="D42">
-        <v>32.83531621921725</v>
+        <v>32.92259432301652</v>
       </c>
       <c r="E42">
-        <v>-1.259999999999998</v>
+        <v>-0.9739999999999984</v>
       </c>
       <c r="F42">
-        <v>11.44</v>
+        <v>11.726</v>
       </c>
       <c r="G42">
         <v>0.406</v>
@@ -4859,28 +4859,28 @@
         <v>4.91</v>
       </c>
       <c r="M42">
-        <v>0.61204</v>
+        <v>0.627341</v>
       </c>
       <c r="N42">
-        <v>4.29796</v>
+        <v>4.282659</v>
       </c>
       <c r="O42">
-        <v>0.859592</v>
+        <v>0.8565318</v>
       </c>
       <c r="P42">
-        <v>3.438368</v>
+        <v>3.4261272</v>
       </c>
       <c r="Q42">
-        <v>8.128367999999998</v>
+        <v>8.116127199999999</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1617137545220885</v>
+        <v>0.1634221370500485</v>
       </c>
       <c r="T42">
-        <v>1.26930312227432</v>
+        <v>1.288010611180353</v>
       </c>
       <c r="U42">
         <v>0.0535</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>8.022351480295406</v>
+        <v>7.826684371019907</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1139670608595286</v>
+        <v>0.1137858690058042</v>
       </c>
       <c r="C43">
-        <v>21.60259432301652</v>
+        <v>21.40433764353355</v>
       </c>
       <c r="D43">
-        <v>32.92259432301652</v>
+        <v>33.01033764353355</v>
       </c>
       <c r="E43">
-        <v>-0.9739999999999984</v>
+        <v>-0.6879999999999971</v>
       </c>
       <c r="F43">
-        <v>11.726</v>
+        <v>12.012</v>
       </c>
       <c r="G43">
         <v>0.406</v>
@@ -4941,28 +4941,28 @@
         <v>4.91</v>
       </c>
       <c r="M43">
-        <v>0.627341</v>
+        <v>0.6426420000000002</v>
       </c>
       <c r="N43">
-        <v>4.282659</v>
+        <v>4.267358</v>
       </c>
       <c r="O43">
-        <v>0.8565318</v>
+        <v>0.8534716</v>
       </c>
       <c r="P43">
-        <v>3.4261272</v>
+        <v>3.4138864</v>
       </c>
       <c r="Q43">
-        <v>8.116127199999999</v>
+        <v>8.1038864</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1634221370500485</v>
+        <v>0.165189429320352</v>
       </c>
       <c r="T43">
-        <v>1.288010611180353</v>
+        <v>1.307363185910732</v>
       </c>
       <c r="U43">
         <v>0.0535</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.826684371019907</v>
+        <v>7.64033474313848</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1137858690058042</v>
+        <v>0.1138798771520797</v>
       </c>
       <c r="C44">
-        <v>21.40433764353356</v>
+        <v>21.072755295568</v>
       </c>
       <c r="D44">
-        <v>33.01033764353356</v>
+        <v>32.964755295568</v>
       </c>
       <c r="E44">
-        <v>-0.6879999999999988</v>
+        <v>-0.4019999999999992</v>
       </c>
       <c r="F44">
-        <v>12.012</v>
+        <v>12.298</v>
       </c>
       <c r="G44">
         <v>0.406</v>
@@ -5023,45 +5023,45 @@
         <v>4.91</v>
       </c>
       <c r="M44">
-        <v>0.642642</v>
+        <v>0.6677814</v>
       </c>
       <c r="N44">
-        <v>4.267358</v>
+        <v>4.2422186</v>
       </c>
       <c r="O44">
-        <v>0.8534716</v>
+        <v>0.8484437200000001</v>
       </c>
       <c r="P44">
-        <v>3.4138864</v>
+        <v>3.39377488</v>
       </c>
       <c r="Q44">
-        <v>8.1038864</v>
+        <v>8.08377488</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.165189429320352</v>
+        <v>0.1670187318457539</v>
       </c>
       <c r="T44">
-        <v>1.307363185910731</v>
+        <v>1.327394798350948</v>
       </c>
       <c r="U44">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V44">
         <v>0.2</v>
       </c>
       <c r="W44">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y44">
-        <v>7.640334743138481</v>
+        <v>7.352705541064786</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1138798771520797</v>
+        <v>0.1137050852983552</v>
       </c>
       <c r="C45">
-        <v>21.072755295568</v>
+        <v>20.87160859720763</v>
       </c>
       <c r="D45">
-        <v>32.964755295568</v>
+        <v>33.04960859720764</v>
       </c>
       <c r="E45">
-        <v>-0.4019999999999992</v>
+        <v>-0.1159999999999979</v>
       </c>
       <c r="F45">
-        <v>12.298</v>
+        <v>12.584</v>
       </c>
       <c r="G45">
         <v>0.406</v>
@@ -5105,28 +5105,28 @@
         <v>4.91</v>
       </c>
       <c r="M45">
-        <v>0.6677814</v>
+        <v>0.6833112000000001</v>
       </c>
       <c r="N45">
-        <v>4.2422186</v>
+        <v>4.2266888</v>
       </c>
       <c r="O45">
-        <v>0.8484437200000001</v>
+        <v>0.84533776</v>
       </c>
       <c r="P45">
-        <v>3.39377488</v>
+        <v>3.38135104</v>
       </c>
       <c r="Q45">
-        <v>8.08377488</v>
+        <v>8.07135104</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1670187318457539</v>
+        <v>0.1689133666042058</v>
       </c>
       <c r="T45">
-        <v>1.327394798350948</v>
+        <v>1.348141825521172</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>7.352705541064786</v>
+        <v>7.185598596949675</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1137050852983552</v>
+        <v>0.1135302934446308</v>
       </c>
       <c r="C46">
-        <v>20.87160859720763</v>
+        <v>20.67089986139351</v>
       </c>
       <c r="D46">
-        <v>33.04960859720764</v>
+        <v>33.13489986139351</v>
       </c>
       <c r="E46">
-        <v>-0.1159999999999979</v>
+        <v>0.1700000000000017</v>
       </c>
       <c r="F46">
-        <v>12.584</v>
+        <v>12.87</v>
       </c>
       <c r="G46">
         <v>0.406</v>
@@ -5187,28 +5187,28 @@
         <v>4.91</v>
       </c>
       <c r="M46">
-        <v>0.6833112000000001</v>
+        <v>0.698841</v>
       </c>
       <c r="N46">
-        <v>4.2266888</v>
+        <v>4.211159</v>
       </c>
       <c r="O46">
-        <v>0.84533776</v>
+        <v>0.8422318000000001</v>
       </c>
       <c r="P46">
-        <v>3.38135104</v>
+        <v>3.3689272</v>
       </c>
       <c r="Q46">
-        <v>8.07135104</v>
+        <v>8.058927199999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1689133666042058</v>
+        <v>0.170876897172056</v>
       </c>
       <c r="T46">
-        <v>1.348141825521172</v>
+        <v>1.369643290043041</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>7.185598596949675</v>
+        <v>7.025918628128573</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1135302934446308</v>
+        <v>0.1133555015909063</v>
       </c>
       <c r="C47">
-        <v>20.67089986139351</v>
+        <v>20.47063248765422</v>
       </c>
       <c r="D47">
-        <v>33.13489986139351</v>
+        <v>33.22063248765422</v>
       </c>
       <c r="E47">
-        <v>0.1700000000000017</v>
+        <v>0.4560000000000013</v>
       </c>
       <c r="F47">
-        <v>12.87</v>
+        <v>13.156</v>
       </c>
       <c r="G47">
         <v>0.406</v>
@@ -5269,28 +5269,28 @@
         <v>4.91</v>
       </c>
       <c r="M47">
-        <v>0.698841</v>
+        <v>0.7143708000000001</v>
       </c>
       <c r="N47">
-        <v>4.211159</v>
+        <v>4.1956292</v>
       </c>
       <c r="O47">
-        <v>0.8422318000000001</v>
+        <v>0.83912584</v>
       </c>
       <c r="P47">
-        <v>3.3689272</v>
+        <v>3.35650336</v>
       </c>
       <c r="Q47">
-        <v>8.058927199999999</v>
+        <v>8.046503359999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.170876897172056</v>
+        <v>0.172913151094271</v>
       </c>
       <c r="T47">
-        <v>1.369643290043041</v>
+        <v>1.391941105102757</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>7.025918628128573</v>
+        <v>6.873181266647516</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1133555015909063</v>
+        <v>0.1131807097371819</v>
       </c>
       <c r="C48">
-        <v>20.47063248765422</v>
+        <v>20.27080991079306</v>
       </c>
       <c r="D48">
-        <v>33.22063248765422</v>
+        <v>33.30680991079306</v>
       </c>
       <c r="E48">
-        <v>0.4560000000000013</v>
+        <v>0.7420000000000027</v>
       </c>
       <c r="F48">
-        <v>13.156</v>
+        <v>13.442</v>
       </c>
       <c r="G48">
         <v>0.406</v>
@@ -5351,28 +5351,28 @@
         <v>4.91</v>
       </c>
       <c r="M48">
-        <v>0.7143708000000001</v>
+        <v>0.7299006000000001</v>
       </c>
       <c r="N48">
-        <v>4.1956292</v>
+        <v>4.1800994</v>
       </c>
       <c r="O48">
-        <v>0.83912584</v>
+        <v>0.8360198799999999</v>
       </c>
       <c r="P48">
-        <v>3.35650336</v>
+        <v>3.34407952</v>
       </c>
       <c r="Q48">
-        <v>8.046503359999999</v>
+        <v>8.034079519999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.172913151094271</v>
+        <v>0.1750262447871356</v>
       </c>
       <c r="T48">
-        <v>1.391941105102757</v>
+        <v>1.415080347145858</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.873181266647516</v>
+        <v>6.726943367357142</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1131807097371819</v>
+        <v>0.1130059178834574</v>
       </c>
       <c r="C49">
-        <v>20.27080991079306</v>
+        <v>20.07143560134685</v>
       </c>
       <c r="D49">
-        <v>33.30680991079306</v>
+        <v>33.39343560134685</v>
       </c>
       <c r="E49">
-        <v>0.7420000000000027</v>
+        <v>1.028000000000002</v>
       </c>
       <c r="F49">
-        <v>13.442</v>
+        <v>13.728</v>
       </c>
       <c r="G49">
         <v>0.406</v>
@@ -5433,28 +5433,28 @@
         <v>4.91</v>
       </c>
       <c r="M49">
-        <v>0.7299006000000001</v>
+        <v>0.7454304</v>
       </c>
       <c r="N49">
-        <v>4.1800994</v>
+        <v>4.1645696</v>
       </c>
       <c r="O49">
-        <v>0.8360198799999999</v>
+        <v>0.8329139200000001</v>
       </c>
       <c r="P49">
-        <v>3.34407952</v>
+        <v>3.33165568</v>
       </c>
       <c r="Q49">
-        <v>8.034079519999999</v>
+        <v>8.021655679999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1750262447871356</v>
+        <v>0.1772206113143411</v>
       </c>
       <c r="T49">
-        <v>1.415080347145858</v>
+        <v>1.439109560036771</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.726943367357142</v>
+        <v>6.586798713870537</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1130059178834574</v>
+        <v>0.1128311260297329</v>
       </c>
       <c r="C50">
-        <v>20.07143560134685</v>
+        <v>19.87251306605181</v>
       </c>
       <c r="D50">
-        <v>33.39343560134685</v>
+        <v>33.48051306605181</v>
       </c>
       <c r="E50">
-        <v>1.028</v>
+        <v>1.314000000000002</v>
       </c>
       <c r="F50">
-        <v>13.728</v>
+        <v>14.014</v>
       </c>
       <c r="G50">
         <v>0.406</v>
@@ -5515,28 +5515,28 @@
         <v>4.91</v>
       </c>
       <c r="M50">
-        <v>0.7454304</v>
+        <v>0.7609602000000001</v>
       </c>
       <c r="N50">
-        <v>4.1645696</v>
+        <v>4.1490398</v>
       </c>
       <c r="O50">
-        <v>0.8329139200000001</v>
+        <v>0.82980796</v>
       </c>
       <c r="P50">
-        <v>3.33165568</v>
+        <v>3.31923184</v>
       </c>
       <c r="Q50">
-        <v>8.021655679999999</v>
+        <v>8.009231839999998</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1772206113143411</v>
+        <v>0.1795010314308489</v>
       </c>
       <c r="T50">
-        <v>1.439109560036771</v>
+        <v>1.464081095001837</v>
       </c>
       <c r="U50">
         <v>0.0543</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>6.586798713870537</v>
+        <v>6.452374250322158</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1128311260297329</v>
+        <v>0.1126563341760085</v>
       </c>
       <c r="C51">
-        <v>19.87251306605181</v>
+        <v>19.67404584831676</v>
       </c>
       <c r="D51">
-        <v>33.48051306605181</v>
+        <v>33.56804584831676</v>
       </c>
       <c r="E51">
-        <v>1.314000000000002</v>
+        <v>1.600000000000001</v>
       </c>
       <c r="F51">
-        <v>14.014</v>
+        <v>14.3</v>
       </c>
       <c r="G51">
         <v>0.406</v>
@@ -5597,28 +5597,28 @@
         <v>4.91</v>
       </c>
       <c r="M51">
-        <v>0.7609602000000001</v>
+        <v>0.77649</v>
       </c>
       <c r="N51">
-        <v>4.1490398</v>
+        <v>4.13351</v>
       </c>
       <c r="O51">
-        <v>0.82980796</v>
+        <v>0.826702</v>
       </c>
       <c r="P51">
-        <v>3.31923184</v>
+        <v>3.306808</v>
       </c>
       <c r="Q51">
-        <v>8.009231839999998</v>
+        <v>7.996808</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1795010314308489</v>
+        <v>0.1818726683520169</v>
       </c>
       <c r="T51">
-        <v>1.464081095001837</v>
+        <v>1.490051491365506</v>
       </c>
       <c r="U51">
         <v>0.0543</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>6.452374250322158</v>
+        <v>6.323326765315715</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1126563341760085</v>
+        <v>0.112481542322284</v>
       </c>
       <c r="C52">
-        <v>19.67404584831676</v>
+        <v>19.47603752870376</v>
       </c>
       <c r="D52">
-        <v>33.56804584831676</v>
+        <v>33.65603752870376</v>
       </c>
       <c r="E52">
-        <v>1.600000000000001</v>
+        <v>1.886000000000001</v>
       </c>
       <c r="F52">
-        <v>14.3</v>
+        <v>14.586</v>
       </c>
       <c r="G52">
         <v>0.406</v>
@@ -5679,28 +5679,28 @@
         <v>4.91</v>
       </c>
       <c r="M52">
-        <v>0.77649</v>
+        <v>0.7920198000000001</v>
       </c>
       <c r="N52">
-        <v>4.13351</v>
+        <v>4.1179802</v>
       </c>
       <c r="O52">
-        <v>0.826702</v>
+        <v>0.82359604</v>
       </c>
       <c r="P52">
-        <v>3.306808</v>
+        <v>3.29438416</v>
       </c>
       <c r="Q52">
-        <v>7.996808</v>
+        <v>7.984384159999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1818726683520169</v>
+        <v>0.1843411067801715</v>
       </c>
       <c r="T52">
-        <v>1.490051491365506</v>
+        <v>1.517081903907284</v>
       </c>
       <c r="U52">
         <v>0.0543</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>6.323326765315715</v>
+        <v>6.199339965995799</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.112481542322284</v>
+        <v>0.1127227504685595</v>
       </c>
       <c r="C53">
-        <v>19.47603752870376</v>
+        <v>19.06873183868895</v>
       </c>
       <c r="D53">
-        <v>33.65603752870376</v>
+        <v>33.53473183868895</v>
       </c>
       <c r="E53">
-        <v>1.886000000000001</v>
+        <v>2.172000000000002</v>
       </c>
       <c r="F53">
-        <v>14.586</v>
+        <v>14.872</v>
       </c>
       <c r="G53">
         <v>0.406</v>
@@ -5761,45 +5761,45 @@
         <v>4.91</v>
       </c>
       <c r="M53">
-        <v>0.7920198000000001</v>
+        <v>0.8224216000000001</v>
       </c>
       <c r="N53">
-        <v>4.1179802</v>
+        <v>4.0875784</v>
       </c>
       <c r="O53">
-        <v>0.82359604</v>
+        <v>0.8175156800000001</v>
       </c>
       <c r="P53">
-        <v>3.29438416</v>
+        <v>3.27006272</v>
       </c>
       <c r="Q53">
-        <v>7.984384159999999</v>
+        <v>7.96006272</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1843411067801715</v>
+        <v>0.186912396809499</v>
       </c>
       <c r="T53">
-        <v>1.517081903907284</v>
+        <v>1.545238583638303</v>
       </c>
       <c r="U53">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V53">
         <v>0.2</v>
       </c>
       <c r="W53">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y53">
-        <v>6.199339965995799</v>
+        <v>5.97017393512038</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1127227504685595</v>
+        <v>0.1125559586148351</v>
       </c>
       <c r="C54">
-        <v>19.06873183868895</v>
+        <v>18.86651941666081</v>
       </c>
       <c r="D54">
-        <v>33.53473183868895</v>
+        <v>33.61851941666082</v>
       </c>
       <c r="E54">
-        <v>2.172000000000002</v>
+        <v>2.458000000000002</v>
       </c>
       <c r="F54">
-        <v>14.872</v>
+        <v>15.158</v>
       </c>
       <c r="G54">
         <v>0.406</v>
@@ -5843,28 +5843,28 @@
         <v>4.91</v>
       </c>
       <c r="M54">
-        <v>0.8224216000000001</v>
+        <v>0.8382374000000001</v>
       </c>
       <c r="N54">
-        <v>4.0875784</v>
+        <v>4.0717626</v>
       </c>
       <c r="O54">
-        <v>0.8175156800000001</v>
+        <v>0.8143525199999999</v>
       </c>
       <c r="P54">
-        <v>3.27006272</v>
+        <v>3.25741008</v>
       </c>
       <c r="Q54">
-        <v>7.96006272</v>
+        <v>7.947410079999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.186912396809499</v>
+        <v>0.1895931034358193</v>
       </c>
       <c r="T54">
-        <v>1.545238583638303</v>
+        <v>1.57459341995362</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.97017393512038</v>
+        <v>5.857529143891694</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1125559586148351</v>
+        <v>0.1123891667611106</v>
       </c>
       <c r="C55">
-        <v>18.86651941666081</v>
+        <v>18.66472673514392</v>
       </c>
       <c r="D55">
-        <v>33.61851941666082</v>
+        <v>33.70272673514392</v>
       </c>
       <c r="E55">
-        <v>2.458000000000002</v>
+        <v>2.744000000000003</v>
       </c>
       <c r="F55">
-        <v>15.158</v>
+        <v>15.444</v>
       </c>
       <c r="G55">
         <v>0.406</v>
@@ -5925,28 +5925,28 @@
         <v>4.91</v>
       </c>
       <c r="M55">
-        <v>0.8382374000000001</v>
+        <v>0.8540532000000002</v>
       </c>
       <c r="N55">
-        <v>4.0717626</v>
+        <v>4.0559468</v>
       </c>
       <c r="O55">
-        <v>0.8143525199999999</v>
+        <v>0.8111893600000001</v>
       </c>
       <c r="P55">
-        <v>3.25741008</v>
+        <v>3.24475744</v>
       </c>
       <c r="Q55">
-        <v>7.947410079999999</v>
+        <v>7.934757439999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1895931034358193</v>
+        <v>0.1923903625241535</v>
       </c>
       <c r="T55">
-        <v>1.57459341995362</v>
+        <v>1.605224553500038</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.857529143891694</v>
+        <v>5.749056381967773</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1123891667611106</v>
+        <v>0.1122223749073862</v>
       </c>
       <c r="C56">
-        <v>18.66472673514392</v>
+        <v>18.46335695614341</v>
       </c>
       <c r="D56">
-        <v>33.70272673514392</v>
+        <v>33.78735695614341</v>
       </c>
       <c r="E56">
-        <v>2.744000000000003</v>
+        <v>3.030000000000003</v>
       </c>
       <c r="F56">
-        <v>15.444</v>
+        <v>15.73</v>
       </c>
       <c r="G56">
         <v>0.406</v>
@@ -6007,28 +6007,28 @@
         <v>4.91</v>
       </c>
       <c r="M56">
-        <v>0.8540532000000002</v>
+        <v>0.8698690000000001</v>
       </c>
       <c r="N56">
-        <v>4.0559468</v>
+        <v>4.040131</v>
       </c>
       <c r="O56">
-        <v>0.8111893600000001</v>
+        <v>0.8080262</v>
       </c>
       <c r="P56">
-        <v>3.24475744</v>
+        <v>3.2321048</v>
       </c>
       <c r="Q56">
-        <v>7.934757439999999</v>
+        <v>7.9221048</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1923903625241535</v>
+        <v>0.1953119442386359</v>
       </c>
       <c r="T56">
-        <v>1.605224553500038</v>
+        <v>1.637217070759631</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.749056381967773</v>
+        <v>5.644528084113814</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1122223749073862</v>
+        <v>0.1120555830536617</v>
       </c>
       <c r="C57">
-        <v>18.46335695614341</v>
+        <v>18.26241327350464</v>
       </c>
       <c r="D57">
-        <v>33.78735695614341</v>
+        <v>33.87241327350464</v>
       </c>
       <c r="E57">
-        <v>3.030000000000003</v>
+        <v>3.316000000000003</v>
       </c>
       <c r="F57">
-        <v>15.73</v>
+        <v>16.016</v>
       </c>
       <c r="G57">
         <v>0.406</v>
@@ -6089,28 +6089,28 @@
         <v>4.91</v>
       </c>
       <c r="M57">
-        <v>0.8698690000000001</v>
+        <v>0.8856848000000002</v>
       </c>
       <c r="N57">
-        <v>4.040131</v>
+        <v>4.0243152</v>
       </c>
       <c r="O57">
-        <v>0.8080262</v>
+        <v>0.8048630400000001</v>
       </c>
       <c r="P57">
-        <v>3.2321048</v>
+        <v>3.21945216</v>
       </c>
       <c r="Q57">
-        <v>7.9221048</v>
+        <v>7.90945216</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1953119442386359</v>
+        <v>0.1983663251219584</v>
       </c>
       <c r="T57">
-        <v>1.637217070759631</v>
+        <v>1.670663793349204</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.644528084113814</v>
+        <v>5.543732939754639</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1120555830536617</v>
+        <v>0.1118887911999372</v>
       </c>
       <c r="C58">
-        <v>18.26241327350464</v>
+        <v>18.06189891331483</v>
       </c>
       <c r="D58">
-        <v>33.87241327350464</v>
+        <v>33.95789891331484</v>
       </c>
       <c r="E58">
-        <v>3.316000000000003</v>
+        <v>3.602000000000004</v>
       </c>
       <c r="F58">
-        <v>16.016</v>
+        <v>16.302</v>
       </c>
       <c r="G58">
         <v>0.406</v>
@@ -6171,28 +6171,28 @@
         <v>4.91</v>
       </c>
       <c r="M58">
-        <v>0.8856848000000002</v>
+        <v>0.9015006000000002</v>
       </c>
       <c r="N58">
-        <v>4.0243152</v>
+        <v>4.0084994</v>
       </c>
       <c r="O58">
-        <v>0.8048630400000001</v>
+        <v>0.80169988</v>
       </c>
       <c r="P58">
-        <v>3.21945216</v>
+        <v>3.20679952</v>
       </c>
       <c r="Q58">
-        <v>7.90945216</v>
+        <v>7.896799519999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1983663251219584</v>
+        <v>0.2015627702324121</v>
       </c>
       <c r="T58">
-        <v>1.670663793349204</v>
+        <v>1.705666177454572</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.543732939754639</v>
+        <v>5.446474467127364</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1118887911999372</v>
+        <v>0.1117219993462128</v>
       </c>
       <c r="C59">
-        <v>18.06189891331483</v>
+        <v>17.86181713431103</v>
       </c>
       <c r="D59">
-        <v>33.95789891331484</v>
+        <v>34.04381713431103</v>
       </c>
       <c r="E59">
-        <v>3.602000000000004</v>
+        <v>3.888000000000005</v>
       </c>
       <c r="F59">
-        <v>16.302</v>
+        <v>16.588</v>
       </c>
       <c r="G59">
         <v>0.406</v>
@@ -6253,28 +6253,28 @@
         <v>4.91</v>
       </c>
       <c r="M59">
-        <v>0.9015006000000002</v>
+        <v>0.9173164000000003</v>
       </c>
       <c r="N59">
-        <v>4.0084994</v>
+        <v>3.9926836</v>
       </c>
       <c r="O59">
-        <v>0.80169988</v>
+        <v>0.79853672</v>
       </c>
       <c r="P59">
-        <v>3.20679952</v>
+        <v>3.19414688</v>
       </c>
       <c r="Q59">
-        <v>7.896799519999999</v>
+        <v>7.884146879999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2015627702324121</v>
+        <v>0.2049114270147923</v>
       </c>
       <c r="T59">
-        <v>1.705666177454572</v>
+        <v>1.742335341755433</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.446474467127364</v>
+        <v>5.352569734935512</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1117219993462128</v>
+        <v>0.1115552074924883</v>
       </c>
       <c r="C60">
-        <v>17.86181713431103</v>
+        <v>17.66217122829419</v>
       </c>
       <c r="D60">
-        <v>34.04381713431103</v>
+        <v>34.13017122829419</v>
       </c>
       <c r="E60">
-        <v>3.888000000000002</v>
+        <v>4.173999999999999</v>
       </c>
       <c r="F60">
-        <v>16.588</v>
+        <v>16.874</v>
       </c>
       <c r="G60">
         <v>0.406</v>
@@ -6335,28 +6335,28 @@
         <v>4.91</v>
       </c>
       <c r="M60">
-        <v>0.9173164</v>
+        <v>0.9331322</v>
       </c>
       <c r="N60">
-        <v>3.9926836</v>
+        <v>3.9768678</v>
       </c>
       <c r="O60">
-        <v>0.7985367200000001</v>
+        <v>0.79537356</v>
       </c>
       <c r="P60">
-        <v>3.19414688</v>
+        <v>3.18149424</v>
       </c>
       <c r="Q60">
-        <v>7.884146879999999</v>
+        <v>7.87149424</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2049114270147923</v>
+        <v>0.208423432908508</v>
       </c>
       <c r="T60">
-        <v>1.742335341755433</v>
+        <v>1.780793245778288</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.352569734935514</v>
+        <v>5.261848214004404</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1115552074924883</v>
+        <v>0.1113884156387638</v>
       </c>
       <c r="C61">
-        <v>17.66217122829419</v>
+        <v>17.46296452054955</v>
       </c>
       <c r="D61">
-        <v>34.13017122829419</v>
+        <v>34.21696452054955</v>
       </c>
       <c r="E61">
-        <v>4.173999999999999</v>
+        <v>4.460000000000001</v>
       </c>
       <c r="F61">
-        <v>16.874</v>
+        <v>17.16</v>
       </c>
       <c r="G61">
         <v>0.406</v>
@@ -6417,28 +6417,28 @@
         <v>4.91</v>
       </c>
       <c r="M61">
-        <v>0.9331322</v>
+        <v>0.948948</v>
       </c>
       <c r="N61">
-        <v>3.9768678</v>
+        <v>3.961052</v>
       </c>
       <c r="O61">
-        <v>0.79537356</v>
+        <v>0.7922104000000001</v>
       </c>
       <c r="P61">
-        <v>3.18149424</v>
+        <v>3.1688416</v>
       </c>
       <c r="Q61">
-        <v>7.87149424</v>
+        <v>7.8588416</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.208423432908508</v>
+        <v>0.2121110390969096</v>
       </c>
       <c r="T61">
-        <v>1.780793245778288</v>
+        <v>1.821174045002285</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>5.261848214004404</v>
+        <v>5.174150743770997</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1113884156387638</v>
+        <v>0.1112216237850394</v>
       </c>
       <c r="C62">
-        <v>17.46296452054955</v>
+        <v>17.26420037027347</v>
       </c>
       <c r="D62">
-        <v>34.21696452054955</v>
+        <v>34.30420037027347</v>
       </c>
       <c r="E62">
-        <v>4.460000000000001</v>
+        <v>4.746000000000002</v>
       </c>
       <c r="F62">
-        <v>17.16</v>
+        <v>17.446</v>
       </c>
       <c r="G62">
         <v>0.406</v>
@@ -6499,28 +6499,28 @@
         <v>4.91</v>
       </c>
       <c r="M62">
-        <v>0.948948</v>
+        <v>0.9647638000000002</v>
       </c>
       <c r="N62">
-        <v>3.961052</v>
+        <v>3.9452362</v>
       </c>
       <c r="O62">
-        <v>0.7922104000000001</v>
+        <v>0.78904724</v>
       </c>
       <c r="P62">
-        <v>3.1688416</v>
+        <v>3.15618896</v>
       </c>
       <c r="Q62">
-        <v>7.8588416</v>
+        <v>7.846188959999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2121110390969096</v>
+        <v>0.2159877532949727</v>
       </c>
       <c r="T62">
-        <v>1.821174045002285</v>
+        <v>1.863625654442898</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>5.174150743770997</v>
+        <v>5.089328600430489</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1112216237850394</v>
+        <v>0.1110548319313149</v>
       </c>
       <c r="C63">
-        <v>17.26420037027347</v>
+        <v>17.06588217100686</v>
       </c>
       <c r="D63">
-        <v>34.30420037027347</v>
+        <v>34.39188217100686</v>
       </c>
       <c r="E63">
-        <v>4.746000000000002</v>
+        <v>5.032</v>
       </c>
       <c r="F63">
-        <v>17.446</v>
+        <v>17.732</v>
       </c>
       <c r="G63">
         <v>0.406</v>
@@ -6581,28 +6581,28 @@
         <v>4.91</v>
       </c>
       <c r="M63">
-        <v>0.9647638000000002</v>
+        <v>0.9805796</v>
       </c>
       <c r="N63">
-        <v>3.9452362</v>
+        <v>3.9294204</v>
       </c>
       <c r="O63">
-        <v>0.78904724</v>
+        <v>0.7858840800000001</v>
       </c>
       <c r="P63">
-        <v>3.15618896</v>
+        <v>3.14353632</v>
       </c>
       <c r="Q63">
-        <v>7.846188959999999</v>
+        <v>7.833536319999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2159877532949727</v>
+        <v>0.2200685050824077</v>
       </c>
       <c r="T63">
-        <v>1.863625654442898</v>
+        <v>1.908311559117227</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>5.089328600430489</v>
+        <v>5.007242655262255</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1110548319313149</v>
+        <v>0.1108880400775905</v>
       </c>
       <c r="C64">
-        <v>17.06588217100686</v>
+        <v>16.86801335107523</v>
       </c>
       <c r="D64">
-        <v>34.39188217100686</v>
+        <v>34.48001335107524</v>
       </c>
       <c r="E64">
-        <v>5.032</v>
+        <v>5.318000000000001</v>
       </c>
       <c r="F64">
-        <v>17.732</v>
+        <v>18.018</v>
       </c>
       <c r="G64">
         <v>0.406</v>
@@ -6663,28 +6663,28 @@
         <v>4.91</v>
       </c>
       <c r="M64">
-        <v>0.9805796</v>
+        <v>0.9963954</v>
       </c>
       <c r="N64">
-        <v>3.9294204</v>
+        <v>3.9136046</v>
       </c>
       <c r="O64">
-        <v>0.7858840800000001</v>
+        <v>0.78272092</v>
       </c>
       <c r="P64">
-        <v>3.14353632</v>
+        <v>3.13088368</v>
       </c>
       <c r="Q64">
-        <v>7.833536319999999</v>
+        <v>7.82088368</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2200685050824077</v>
+        <v>0.2243698380475418</v>
       </c>
       <c r="T64">
-        <v>1.908311559117227</v>
+        <v>1.955412918098277</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>5.007242655262255</v>
+        <v>4.927762613115235</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1108880400775905</v>
+        <v>0.110721248223866</v>
       </c>
       <c r="C65">
-        <v>16.86801335107523</v>
+        <v>16.67059737403546</v>
       </c>
       <c r="D65">
-        <v>34.48001335107524</v>
+        <v>34.56859737403546</v>
       </c>
       <c r="E65">
-        <v>5.318000000000001</v>
+        <v>5.604000000000003</v>
       </c>
       <c r="F65">
-        <v>18.018</v>
+        <v>18.304</v>
       </c>
       <c r="G65">
         <v>0.406</v>
@@ -6745,28 +6745,28 @@
         <v>4.91</v>
       </c>
       <c r="M65">
-        <v>0.9963954</v>
+        <v>1.0122112</v>
       </c>
       <c r="N65">
-        <v>3.9136046</v>
+        <v>3.8977888</v>
       </c>
       <c r="O65">
-        <v>0.78272092</v>
+        <v>0.77955776</v>
       </c>
       <c r="P65">
-        <v>3.13088368</v>
+        <v>3.11823104</v>
       </c>
       <c r="Q65">
-        <v>7.82088368</v>
+        <v>7.808231039999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2243698380475418</v>
+        <v>0.2289101339551833</v>
       </c>
       <c r="T65">
-        <v>1.955412918098277</v>
+        <v>2.005131019244941</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.927762613115235</v>
+        <v>4.85076632228531</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.110721248223866</v>
+        <v>0.1105544563701415</v>
       </c>
       <c r="C66">
-        <v>16.67059737403546</v>
+        <v>16.47363773912963</v>
       </c>
       <c r="D66">
-        <v>34.56859737403546</v>
+        <v>34.65763773912963</v>
       </c>
       <c r="E66">
-        <v>5.604000000000003</v>
+        <v>5.890000000000001</v>
       </c>
       <c r="F66">
-        <v>18.304</v>
+        <v>18.59</v>
       </c>
       <c r="G66">
         <v>0.406</v>
@@ -6827,28 +6827,28 @@
         <v>4.91</v>
       </c>
       <c r="M66">
-        <v>1.0122112</v>
+        <v>1.028027</v>
       </c>
       <c r="N66">
-        <v>3.8977888</v>
+        <v>3.881973</v>
       </c>
       <c r="O66">
-        <v>0.77955776</v>
+        <v>0.7763946000000002</v>
       </c>
       <c r="P66">
-        <v>3.11823104</v>
+        <v>3.1055784</v>
       </c>
       <c r="Q66">
-        <v>7.808231039999999</v>
+        <v>7.7955784</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2289101339551833</v>
+        <v>0.2337098753432615</v>
       </c>
       <c r="T66">
-        <v>2.005131019244941</v>
+        <v>2.057690154742842</v>
       </c>
       <c r="U66">
         <v>0.0553</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>4.85076632228531</v>
+        <v>4.776139148096306</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1105544563701415</v>
+        <v>0.110387664516417</v>
       </c>
       <c r="C67">
-        <v>16.47363773912963</v>
+        <v>16.27713798174562</v>
       </c>
       <c r="D67">
-        <v>34.65763773912963</v>
+        <v>34.74713798174562</v>
       </c>
       <c r="E67">
-        <v>5.890000000000001</v>
+        <v>6.176000000000002</v>
       </c>
       <c r="F67">
-        <v>18.59</v>
+        <v>18.876</v>
       </c>
       <c r="G67">
         <v>0.406</v>
@@ -6909,28 +6909,28 @@
         <v>4.91</v>
       </c>
       <c r="M67">
-        <v>1.028027</v>
+        <v>1.0438428</v>
       </c>
       <c r="N67">
-        <v>3.881973</v>
+        <v>3.8661572</v>
       </c>
       <c r="O67">
-        <v>0.7763946000000002</v>
+        <v>0.77323144</v>
       </c>
       <c r="P67">
-        <v>3.1055784</v>
+        <v>3.09292576</v>
       </c>
       <c r="Q67">
-        <v>7.7955784</v>
+        <v>7.782925759999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2337098753432615</v>
+        <v>0.2387919544600502</v>
       </c>
       <c r="T67">
-        <v>2.057690154742842</v>
+        <v>2.113341004093561</v>
       </c>
       <c r="U67">
         <v>0.0553</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.776139148096306</v>
+        <v>4.703773403428178</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.110387664516417</v>
+        <v>0.1102208726626926</v>
       </c>
       <c r="C68">
-        <v>16.27713798174562</v>
+        <v>16.08110167388528</v>
       </c>
       <c r="D68">
-        <v>34.74713798174562</v>
+        <v>34.83710167388529</v>
       </c>
       <c r="E68">
-        <v>6.176000000000002</v>
+        <v>6.462000000000003</v>
       </c>
       <c r="F68">
-        <v>18.876</v>
+        <v>19.162</v>
       </c>
       <c r="G68">
         <v>0.406</v>
@@ -6991,28 +6991,28 @@
         <v>4.91</v>
       </c>
       <c r="M68">
-        <v>1.0438428</v>
+        <v>1.0596586</v>
       </c>
       <c r="N68">
-        <v>3.8661572</v>
+        <v>3.8503414</v>
       </c>
       <c r="O68">
-        <v>0.77323144</v>
+        <v>0.77006828</v>
       </c>
       <c r="P68">
-        <v>3.09292576</v>
+        <v>3.08027312</v>
       </c>
       <c r="Q68">
-        <v>7.782925759999999</v>
+        <v>7.77027312</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2387919544600502</v>
+        <v>0.2441820383717958</v>
       </c>
       <c r="T68">
-        <v>2.113341004093561</v>
+        <v>2.172364632192809</v>
       </c>
       <c r="U68">
         <v>0.0553</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.703773403428178</v>
+        <v>4.633567830242683</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1102208726626926</v>
+        <v>0.1100540808089681</v>
       </c>
       <c r="C69">
-        <v>16.08110167388528</v>
+        <v>15.88553242463948</v>
       </c>
       <c r="D69">
-        <v>34.83710167388529</v>
+        <v>34.92753242463948</v>
       </c>
       <c r="E69">
-        <v>6.462000000000003</v>
+        <v>6.748000000000005</v>
       </c>
       <c r="F69">
-        <v>19.162</v>
+        <v>19.448</v>
       </c>
       <c r="G69">
         <v>0.406</v>
@@ -7073,28 +7073,28 @@
         <v>4.91</v>
       </c>
       <c r="M69">
-        <v>1.0596586</v>
+        <v>1.0754744</v>
       </c>
       <c r="N69">
-        <v>3.8503414</v>
+        <v>3.8345256</v>
       </c>
       <c r="O69">
-        <v>0.77006828</v>
+        <v>0.7669051200000001</v>
       </c>
       <c r="P69">
-        <v>3.08027312</v>
+        <v>3.06762048</v>
       </c>
       <c r="Q69">
-        <v>7.77027312</v>
+        <v>7.75762048</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2441820383717958</v>
+        <v>0.2499090025280254</v>
       </c>
       <c r="T69">
-        <v>2.172364632192809</v>
+        <v>2.235077237048259</v>
       </c>
       <c r="U69">
         <v>0.0553</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.633567830242683</v>
+        <v>4.565427126856761</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1100540808089681</v>
+        <v>0.1112672889552437</v>
       </c>
       <c r="C70">
-        <v>15.88553242463948</v>
+        <v>14.95227228078588</v>
       </c>
       <c r="D70">
-        <v>34.92753242463948</v>
+        <v>34.28027228078589</v>
       </c>
       <c r="E70">
-        <v>6.748000000000005</v>
+        <v>7.034000000000002</v>
       </c>
       <c r="F70">
-        <v>19.448</v>
+        <v>19.734</v>
       </c>
       <c r="G70">
         <v>0.406</v>
@@ -7155,45 +7155,45 @@
         <v>4.91</v>
       </c>
       <c r="M70">
-        <v>1.0754744</v>
+        <v>1.1406252</v>
       </c>
       <c r="N70">
-        <v>3.8345256</v>
+        <v>3.7693748</v>
       </c>
       <c r="O70">
-        <v>0.7669051200000001</v>
+        <v>0.7538749600000001</v>
       </c>
       <c r="P70">
-        <v>3.06762048</v>
+        <v>3.01549984</v>
       </c>
       <c r="Q70">
-        <v>7.75762048</v>
+        <v>7.70549984</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2499090025280254</v>
+        <v>0.2560054482427215</v>
       </c>
       <c r="T70">
-        <v>2.235077237048259</v>
+        <v>2.301835816410513</v>
       </c>
       <c r="U70">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V70">
         <v>0.2</v>
       </c>
       <c r="W70">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y70">
-        <v>4.565427126856761</v>
+        <v>4.304656779457441</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1112672889552437</v>
+        <v>0.1111204971015192</v>
       </c>
       <c r="C71">
-        <v>14.95227228078588</v>
+        <v>14.74330881506784</v>
       </c>
       <c r="D71">
-        <v>34.28027228078589</v>
+        <v>34.35730881506785</v>
       </c>
       <c r="E71">
-        <v>7.034000000000002</v>
+        <v>7.320000000000004</v>
       </c>
       <c r="F71">
-        <v>19.734</v>
+        <v>20.02</v>
       </c>
       <c r="G71">
         <v>0.406</v>
@@ -7237,28 +7237,28 @@
         <v>4.91</v>
       </c>
       <c r="M71">
-        <v>1.1406252</v>
+        <v>1.157156</v>
       </c>
       <c r="N71">
-        <v>3.7693748</v>
+        <v>3.752844</v>
       </c>
       <c r="O71">
-        <v>0.7538749600000001</v>
+        <v>0.7505687999999999</v>
       </c>
       <c r="P71">
-        <v>3.01549984</v>
+        <v>3.0022752</v>
       </c>
       <c r="Q71">
-        <v>7.70549984</v>
+        <v>7.692275199999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2560054482427215</v>
+        <v>0.2625083236717307</v>
       </c>
       <c r="T71">
-        <v>2.301835816410513</v>
+        <v>2.373044967730251</v>
       </c>
       <c r="U71">
         <v>0.0578</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>4.304656779457441</v>
+        <v>4.243161682608048</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1111204971015192</v>
+        <v>0.1109737052477947</v>
       </c>
       <c r="C72">
-        <v>14.74330881506784</v>
+        <v>14.53469237076369</v>
       </c>
       <c r="D72">
-        <v>34.35730881506785</v>
+        <v>34.43469237076369</v>
       </c>
       <c r="E72">
-        <v>7.320000000000004</v>
+        <v>7.606000000000005</v>
       </c>
       <c r="F72">
-        <v>20.02</v>
+        <v>20.306</v>
       </c>
       <c r="G72">
         <v>0.406</v>
@@ -7319,28 +7319,28 @@
         <v>4.91</v>
       </c>
       <c r="M72">
-        <v>1.157156</v>
+        <v>1.1736868</v>
       </c>
       <c r="N72">
-        <v>3.752844</v>
+        <v>3.7363132</v>
       </c>
       <c r="O72">
-        <v>0.7505687999999999</v>
+        <v>0.74726264</v>
       </c>
       <c r="P72">
-        <v>3.0022752</v>
+        <v>2.98905056</v>
       </c>
       <c r="Q72">
-        <v>7.692275199999999</v>
+        <v>7.679050559999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2625083236717307</v>
+        <v>0.2694596732682578</v>
       </c>
       <c r="T72">
-        <v>2.373044967730251</v>
+        <v>2.449165095003074</v>
       </c>
       <c r="U72">
         <v>0.0578</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>4.243161682608048</v>
+        <v>4.183398842007935</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1109737052477947</v>
+        <v>0.1108269133940703</v>
       </c>
       <c r="C73">
-        <v>14.53469237076369</v>
+        <v>14.32642529797344</v>
       </c>
       <c r="D73">
-        <v>34.43469237076369</v>
+        <v>34.51242529797344</v>
       </c>
       <c r="E73">
-        <v>7.606000000000002</v>
+        <v>7.891999999999999</v>
       </c>
       <c r="F73">
-        <v>20.306</v>
+        <v>20.592</v>
       </c>
       <c r="G73">
         <v>0.406</v>
@@ -7401,28 +7401,28 @@
         <v>4.91</v>
       </c>
       <c r="M73">
-        <v>1.1736868</v>
+        <v>1.1902176</v>
       </c>
       <c r="N73">
-        <v>3.7363132</v>
+        <v>3.7197824</v>
       </c>
       <c r="O73">
-        <v>0.7472626400000001</v>
+        <v>0.74395648</v>
       </c>
       <c r="P73">
-        <v>2.98905056</v>
+        <v>2.97582592</v>
       </c>
       <c r="Q73">
-        <v>7.679050559999999</v>
+        <v>7.66582592</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2694596732682576</v>
+        <v>0.2769075478359652</v>
       </c>
       <c r="T73">
-        <v>2.449165095003073</v>
+        <v>2.530722374223955</v>
       </c>
       <c r="U73">
         <v>0.0578</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>4.183398842007936</v>
+        <v>4.125296080313381</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1108269133940703</v>
+        <v>0.1106801215403458</v>
       </c>
       <c r="C74">
-        <v>14.32642529797344</v>
+        <v>14.1185099680656</v>
       </c>
       <c r="D74">
-        <v>34.51242529797344</v>
+        <v>34.5905099680656</v>
       </c>
       <c r="E74">
-        <v>7.891999999999999</v>
+        <v>8.178000000000001</v>
       </c>
       <c r="F74">
-        <v>20.592</v>
+        <v>20.878</v>
       </c>
       <c r="G74">
         <v>0.406</v>
@@ -7483,28 +7483,28 @@
         <v>4.91</v>
       </c>
       <c r="M74">
-        <v>1.1902176</v>
+        <v>1.2067484</v>
       </c>
       <c r="N74">
-        <v>3.7197824</v>
+        <v>3.7032516</v>
       </c>
       <c r="O74">
-        <v>0.74395648</v>
+        <v>0.74065032</v>
       </c>
       <c r="P74">
-        <v>2.97582592</v>
+        <v>2.96260128</v>
       </c>
       <c r="Q74">
-        <v>7.66582592</v>
+        <v>7.652601279999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2769075478359652</v>
+        <v>0.2849071168160955</v>
       </c>
       <c r="T74">
-        <v>2.530722374223955</v>
+        <v>2.618320933387123</v>
       </c>
       <c r="U74">
         <v>0.0578</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>4.125296080313381</v>
+        <v>4.068785175103608</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1106801215403458</v>
+        <v>0.1105333296866213</v>
       </c>
       <c r="C75">
-        <v>14.1185099680656</v>
+        <v>13.91094877391829</v>
       </c>
       <c r="D75">
-        <v>34.5905099680656</v>
+        <v>34.6689487739183</v>
       </c>
       <c r="E75">
-        <v>8.178000000000001</v>
+        <v>8.464000000000002</v>
       </c>
       <c r="F75">
-        <v>20.878</v>
+        <v>21.164</v>
       </c>
       <c r="G75">
         <v>0.406</v>
@@ -7565,28 +7565,28 @@
         <v>4.91</v>
       </c>
       <c r="M75">
-        <v>1.2067484</v>
+        <v>1.2232792</v>
       </c>
       <c r="N75">
-        <v>3.7032516</v>
+        <v>3.6867208</v>
       </c>
       <c r="O75">
-        <v>0.74065032</v>
+        <v>0.73734416</v>
       </c>
       <c r="P75">
-        <v>2.96260128</v>
+        <v>2.94937664</v>
       </c>
       <c r="Q75">
-        <v>7.652601279999999</v>
+        <v>7.639376639999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2849071168160955</v>
+        <v>0.2935220372562359</v>
       </c>
       <c r="T75">
-        <v>2.618320933387123</v>
+        <v>2.712657843255152</v>
       </c>
       <c r="U75">
         <v>0.0578</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>4.068785175103608</v>
+        <v>4.013801591656263</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1105333296866213</v>
+        <v>0.1124865378328969</v>
       </c>
       <c r="C76">
-        <v>13.91094877391829</v>
+        <v>12.6095163437971</v>
       </c>
       <c r="D76">
-        <v>34.6689487739183</v>
+        <v>33.6535163437971</v>
       </c>
       <c r="E76">
-        <v>8.464000000000002</v>
+        <v>8.750000000000004</v>
       </c>
       <c r="F76">
-        <v>21.164</v>
+        <v>21.45</v>
       </c>
       <c r="G76">
         <v>0.406</v>
@@ -7647,45 +7647,45 @@
         <v>4.91</v>
       </c>
       <c r="M76">
-        <v>1.2232792</v>
+        <v>1.314885</v>
       </c>
       <c r="N76">
-        <v>3.6867208</v>
+        <v>3.595115</v>
       </c>
       <c r="O76">
-        <v>0.73734416</v>
+        <v>0.719023</v>
       </c>
       <c r="P76">
-        <v>2.94937664</v>
+        <v>2.876092</v>
       </c>
       <c r="Q76">
-        <v>7.639376639999999</v>
+        <v>7.566091999999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2935220372562359</v>
+        <v>0.3028261513315875</v>
       </c>
       <c r="T76">
-        <v>2.712657843255152</v>
+        <v>2.814541705912623</v>
       </c>
       <c r="U76">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V76">
         <v>0.2</v>
       </c>
       <c r="W76">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y76">
-        <v>4.013801591656263</v>
+        <v>3.734166866303897</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1124865378328969</v>
+        <v>0.1123677459791724</v>
       </c>
       <c r="C77">
-        <v>12.6095163437971</v>
+        <v>12.38357190872604</v>
       </c>
       <c r="D77">
-        <v>33.6535163437971</v>
+        <v>33.71357190872605</v>
       </c>
       <c r="E77">
-        <v>8.750000000000004</v>
+        <v>9.036000000000001</v>
       </c>
       <c r="F77">
-        <v>21.45</v>
+        <v>21.736</v>
       </c>
       <c r="G77">
         <v>0.406</v>
@@ -7729,28 +7729,28 @@
         <v>4.91</v>
       </c>
       <c r="M77">
-        <v>1.314885</v>
+        <v>1.3324168</v>
       </c>
       <c r="N77">
-        <v>3.595115</v>
+        <v>3.5775832</v>
       </c>
       <c r="O77">
-        <v>0.719023</v>
+        <v>0.7155166400000001</v>
       </c>
       <c r="P77">
-        <v>2.876092</v>
+        <v>2.86206656</v>
       </c>
       <c r="Q77">
-        <v>7.566091999999999</v>
+        <v>7.55206656</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3028261513315875</v>
+        <v>0.3129056082465518</v>
       </c>
       <c r="T77">
-        <v>2.814541705912623</v>
+        <v>2.924915890458216</v>
       </c>
       <c r="U77">
         <v>0.0613</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.734166866303897</v>
+        <v>3.685033091747267</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1123677459791724</v>
+        <v>0.112248954125448</v>
       </c>
       <c r="C78">
-        <v>12.38357190872604</v>
+        <v>12.15784219823503</v>
       </c>
       <c r="D78">
-        <v>33.71357190872605</v>
+        <v>33.77384219823504</v>
       </c>
       <c r="E78">
-        <v>9.036000000000001</v>
+        <v>9.322000000000003</v>
       </c>
       <c r="F78">
-        <v>21.736</v>
+        <v>22.022</v>
       </c>
       <c r="G78">
         <v>0.406</v>
@@ -7811,28 +7811,28 @@
         <v>4.91</v>
       </c>
       <c r="M78">
-        <v>1.3324168</v>
+        <v>1.3499486</v>
       </c>
       <c r="N78">
-        <v>3.5775832</v>
+        <v>3.5600514</v>
       </c>
       <c r="O78">
-        <v>0.7155166400000001</v>
+        <v>0.71201028</v>
       </c>
       <c r="P78">
-        <v>2.86206656</v>
+        <v>2.84804112</v>
       </c>
       <c r="Q78">
-        <v>7.55206656</v>
+        <v>7.538041119999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3129056082465518</v>
+        <v>0.3238615396758607</v>
       </c>
       <c r="T78">
-        <v>2.924915890458216</v>
+        <v>3.044887830181687</v>
       </c>
       <c r="U78">
         <v>0.0613</v>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.685033091747267</v>
+        <v>3.637175519127172</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.112248954125448</v>
+        <v>0.1121301622717235</v>
       </c>
       <c r="C79">
-        <v>12.15784219823503</v>
+        <v>11.93232836598615</v>
       </c>
       <c r="D79">
-        <v>33.77384219823504</v>
+        <v>33.83432836598615</v>
       </c>
       <c r="E79">
-        <v>9.322000000000003</v>
+        <v>9.608000000000004</v>
       </c>
       <c r="F79">
-        <v>22.022</v>
+        <v>22.308</v>
       </c>
       <c r="G79">
         <v>0.406</v>
@@ -7893,28 +7893,28 @@
         <v>4.91</v>
       </c>
       <c r="M79">
-        <v>1.3499486</v>
+        <v>1.3674804</v>
       </c>
       <c r="N79">
-        <v>3.5600514</v>
+        <v>3.5425196</v>
       </c>
       <c r="O79">
-        <v>0.71201028</v>
+        <v>0.7085039200000001</v>
       </c>
       <c r="P79">
-        <v>2.84804112</v>
+        <v>2.83401568</v>
       </c>
       <c r="Q79">
-        <v>7.538041119999999</v>
+        <v>7.52401568</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3238615396758607</v>
+        <v>0.3358134648714705</v>
       </c>
       <c r="T79">
-        <v>3.044887830181687</v>
+        <v>3.175766309880018</v>
       </c>
       <c r="U79">
         <v>0.0613</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.637175519127172</v>
+        <v>3.590545063753747</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1121301622717235</v>
+        <v>0.112011370417999</v>
       </c>
       <c r="C80">
-        <v>11.93232836598615</v>
+        <v>11.70703157392074</v>
       </c>
       <c r="D80">
-        <v>33.83432836598615</v>
+        <v>33.89503157392075</v>
       </c>
       <c r="E80">
-        <v>9.608000000000004</v>
+        <v>9.894000000000002</v>
       </c>
       <c r="F80">
-        <v>22.308</v>
+        <v>22.594</v>
       </c>
       <c r="G80">
         <v>0.406</v>
@@ -7975,28 +7975,28 @@
         <v>4.91</v>
       </c>
       <c r="M80">
-        <v>1.3674804</v>
+        <v>1.3850122</v>
       </c>
       <c r="N80">
-        <v>3.5425196</v>
+        <v>3.5249878</v>
       </c>
       <c r="O80">
-        <v>0.7085039200000001</v>
+        <v>0.70499756</v>
       </c>
       <c r="P80">
-        <v>2.83401568</v>
+        <v>2.81999024</v>
       </c>
       <c r="Q80">
-        <v>7.52401568</v>
+        <v>7.50999024</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3358134648714705</v>
+        <v>0.3489036686571383</v>
       </c>
       <c r="T80">
-        <v>3.175766309880018</v>
+        <v>3.319109406692477</v>
       </c>
       <c r="U80">
         <v>0.0613</v>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.590545063753747</v>
+        <v>3.545095126237877</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.112011370417999</v>
+        <v>0.1118925785642746</v>
       </c>
       <c r="C81">
-        <v>11.70703157392074</v>
+        <v>11.48195299233386</v>
       </c>
       <c r="D81">
-        <v>33.89503157392075</v>
+        <v>33.95595299233386</v>
       </c>
       <c r="E81">
-        <v>9.894000000000002</v>
+        <v>10.18</v>
       </c>
       <c r="F81">
-        <v>22.594</v>
+        <v>22.88</v>
       </c>
       <c r="G81">
         <v>0.406</v>
@@ -8057,28 +8057,28 @@
         <v>4.91</v>
       </c>
       <c r="M81">
-        <v>1.3850122</v>
+        <v>1.402544</v>
       </c>
       <c r="N81">
-        <v>3.5249878</v>
+        <v>3.507456</v>
       </c>
       <c r="O81">
-        <v>0.70499756</v>
+        <v>0.7014912</v>
       </c>
       <c r="P81">
-        <v>2.81999024</v>
+        <v>2.8059648</v>
       </c>
       <c r="Q81">
-        <v>7.50999024</v>
+        <v>7.495964799999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3489036686571383</v>
+        <v>0.3633028928213728</v>
       </c>
       <c r="T81">
-        <v>3.319109406692477</v>
+        <v>3.476786813186182</v>
       </c>
       <c r="U81">
         <v>0.0613</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.545095126237877</v>
+        <v>3.500781437159903</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1118925785642746</v>
+        <v>0.1135881867105501</v>
       </c>
       <c r="C82">
-        <v>11.48195299233386</v>
+        <v>10.34660160380659</v>
       </c>
       <c r="D82">
-        <v>33.95595299233386</v>
+        <v>33.1066016038066</v>
       </c>
       <c r="E82">
-        <v>10.18</v>
+        <v>10.466</v>
       </c>
       <c r="F82">
-        <v>22.88</v>
+        <v>23.166</v>
       </c>
       <c r="G82">
         <v>0.406</v>
@@ -8139,45 +8139,45 @@
         <v>4.91</v>
       </c>
       <c r="M82">
-        <v>1.402544</v>
+        <v>1.4849406</v>
       </c>
       <c r="N82">
-        <v>3.507456</v>
+        <v>3.4250594</v>
       </c>
       <c r="O82">
-        <v>0.7014912</v>
+        <v>0.68501188</v>
       </c>
       <c r="P82">
-        <v>2.8059648</v>
+        <v>2.74004752</v>
       </c>
       <c r="Q82">
-        <v>7.495964799999999</v>
+        <v>7.43004752</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3633028928213728</v>
+        <v>0.379217824792369</v>
       </c>
       <c r="T82">
-        <v>3.476786813186182</v>
+        <v>3.651061841416066</v>
       </c>
       <c r="U82">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V82">
         <v>0.2</v>
       </c>
       <c r="W82">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y82">
-        <v>3.500781437159903</v>
+        <v>3.306529567580009</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1135881867105501</v>
+        <v>0.1134917948568256</v>
       </c>
       <c r="C83">
-        <v>10.34660160380659</v>
+        <v>10.10774478719918</v>
       </c>
       <c r="D83">
-        <v>33.1066016038066</v>
+        <v>33.15374478719918</v>
       </c>
       <c r="E83">
-        <v>10.466</v>
+        <v>10.752</v>
       </c>
       <c r="F83">
-        <v>23.166</v>
+        <v>23.452</v>
       </c>
       <c r="G83">
         <v>0.406</v>
@@ -8221,28 +8221,28 @@
         <v>4.91</v>
       </c>
       <c r="M83">
-        <v>1.4849406</v>
+        <v>1.5032732</v>
       </c>
       <c r="N83">
-        <v>3.4250594</v>
+        <v>3.4067268</v>
       </c>
       <c r="O83">
-        <v>0.68501188</v>
+        <v>0.68134536</v>
       </c>
       <c r="P83">
-        <v>2.74004752</v>
+        <v>2.72538144</v>
       </c>
       <c r="Q83">
-        <v>7.43004752</v>
+        <v>7.415381439999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.379217824792369</v>
+        <v>0.3969010825379203</v>
       </c>
       <c r="T83">
-        <v>3.651061841416066</v>
+        <v>3.844700761671492</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.306529567580009</v>
+        <v>3.266206036268058</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1134917948568256</v>
+        <v>0.1133954030031012</v>
       </c>
       <c r="C84">
-        <v>10.10774478719918</v>
+        <v>9.869022424079294</v>
       </c>
       <c r="D84">
-        <v>33.15374478719918</v>
+        <v>33.2010224240793</v>
       </c>
       <c r="E84">
-        <v>10.752</v>
+        <v>11.038</v>
       </c>
       <c r="F84">
-        <v>23.452</v>
+        <v>23.738</v>
       </c>
       <c r="G84">
         <v>0.406</v>
@@ -8303,28 +8303,28 @@
         <v>4.91</v>
       </c>
       <c r="M84">
-        <v>1.5032732</v>
+        <v>1.5216058</v>
       </c>
       <c r="N84">
-        <v>3.4067268</v>
+        <v>3.3883942</v>
       </c>
       <c r="O84">
-        <v>0.68134536</v>
+        <v>0.67767884</v>
       </c>
       <c r="P84">
-        <v>2.72538144</v>
+        <v>2.71071536</v>
       </c>
       <c r="Q84">
-        <v>7.415381439999999</v>
+        <v>7.40071536</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3969010825379203</v>
+        <v>0.4166647235476541</v>
       </c>
       <c r="T84">
-        <v>3.844700761671492</v>
+        <v>4.061120731368734</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.266206036268058</v>
+        <v>3.226854156313021</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1133954030031012</v>
+        <v>0.1132990111493767</v>
       </c>
       <c r="C85">
-        <v>9.869022424079294</v>
+        <v>9.630435090465195</v>
       </c>
       <c r="D85">
-        <v>33.2010224240793</v>
+        <v>33.2484350904652</v>
       </c>
       <c r="E85">
-        <v>11.038</v>
+        <v>11.32400000000001</v>
       </c>
       <c r="F85">
-        <v>23.738</v>
+        <v>24.024</v>
       </c>
       <c r="G85">
         <v>0.406</v>
@@ -8385,28 +8385,28 @@
         <v>4.91</v>
       </c>
       <c r="M85">
-        <v>1.5216058</v>
+        <v>1.5399384</v>
       </c>
       <c r="N85">
-        <v>3.3883942</v>
+        <v>3.3700616</v>
       </c>
       <c r="O85">
-        <v>0.67767884</v>
+        <v>0.67401232</v>
       </c>
       <c r="P85">
-        <v>2.71071536</v>
+        <v>2.69604928</v>
       </c>
       <c r="Q85">
-        <v>7.40071536</v>
+        <v>7.386049279999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4166647235476541</v>
+        <v>0.4388988196836047</v>
       </c>
       <c r="T85">
-        <v>4.061120731368734</v>
+        <v>4.304593197278131</v>
       </c>
       <c r="U85">
         <v>0.0641</v>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>3.226854156313021</v>
+        <v>3.188439225880723</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1132990111493767</v>
+        <v>0.1132026192956523</v>
       </c>
       <c r="C86">
-        <v>9.630435090465205</v>
+        <v>9.3919833656702</v>
       </c>
       <c r="D86">
-        <v>33.24843509046521</v>
+        <v>33.2959833656702</v>
       </c>
       <c r="E86">
-        <v>11.324</v>
+        <v>11.61</v>
       </c>
       <c r="F86">
-        <v>24.024</v>
+        <v>24.31</v>
       </c>
       <c r="G86">
         <v>0.406</v>
@@ -8467,28 +8467,28 @@
         <v>4.91</v>
       </c>
       <c r="M86">
-        <v>1.5399384</v>
+        <v>1.558271</v>
       </c>
       <c r="N86">
-        <v>3.3700616</v>
+        <v>3.351729</v>
       </c>
       <c r="O86">
-        <v>0.67401232</v>
+        <v>0.6703458</v>
       </c>
       <c r="P86">
-        <v>2.69604928</v>
+        <v>2.6813832</v>
       </c>
       <c r="Q86">
-        <v>7.386049279999999</v>
+        <v>7.371383199999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4388988196836044</v>
+        <v>0.464097461971015</v>
       </c>
       <c r="T86">
-        <v>4.304593197278129</v>
+        <v>4.580528658642112</v>
       </c>
       <c r="U86">
         <v>0.0641</v>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>3.188439225880723</v>
+        <v>3.150928176164479</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1132026192956523</v>
+        <v>0.1131062274419278</v>
       </c>
       <c r="C87">
-        <v>9.3919833656702</v>
+        <v>9.153667832326196</v>
       </c>
       <c r="D87">
-        <v>33.2959833656702</v>
+        <v>33.3436678323262</v>
       </c>
       <c r="E87">
-        <v>11.61</v>
+        <v>11.896</v>
       </c>
       <c r="F87">
-        <v>24.31</v>
+        <v>24.596</v>
       </c>
       <c r="G87">
         <v>0.406</v>
@@ -8549,28 +8549,28 @@
         <v>4.91</v>
       </c>
       <c r="M87">
-        <v>1.558271</v>
+        <v>1.5766036</v>
       </c>
       <c r="N87">
-        <v>3.351729</v>
+        <v>3.3333964</v>
       </c>
       <c r="O87">
-        <v>0.6703458</v>
+        <v>0.66667928</v>
       </c>
       <c r="P87">
-        <v>2.6813832</v>
+        <v>2.66671712</v>
       </c>
       <c r="Q87">
-        <v>7.371383199999999</v>
+        <v>7.356717119999999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.464097461971015</v>
+        <v>0.4928959102994842</v>
       </c>
       <c r="T87">
-        <v>4.580528658642112</v>
+        <v>4.895883471629521</v>
       </c>
       <c r="U87">
         <v>0.0641</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>3.150928176164479</v>
+        <v>3.114289476441637</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1131062274419278</v>
+        <v>0.1130098355882033</v>
       </c>
       <c r="C88">
-        <v>9.153667832326196</v>
+        <v>8.915489076407564</v>
       </c>
       <c r="D88">
-        <v>33.3436678323262</v>
+        <v>33.39148907640757</v>
       </c>
       <c r="E88">
-        <v>11.896</v>
+        <v>12.182</v>
       </c>
       <c r="F88">
-        <v>24.596</v>
+        <v>24.882</v>
       </c>
       <c r="G88">
         <v>0.406</v>
@@ -8631,28 +8631,28 @@
         <v>4.91</v>
       </c>
       <c r="M88">
-        <v>1.5766036</v>
+        <v>1.5949362</v>
       </c>
       <c r="N88">
-        <v>3.3333964</v>
+        <v>3.3150638</v>
       </c>
       <c r="O88">
-        <v>0.66667928</v>
+        <v>0.66301276</v>
       </c>
       <c r="P88">
-        <v>2.66671712</v>
+        <v>2.65205104</v>
       </c>
       <c r="Q88">
-        <v>7.356717119999999</v>
+        <v>7.342051039999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4928959102994842</v>
+        <v>0.5261248891400254</v>
       </c>
       <c r="T88">
-        <v>4.895883471629521</v>
+        <v>5.259754409691914</v>
       </c>
       <c r="U88">
         <v>0.0641</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>3.114289476441637</v>
+        <v>3.07849304567794</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1130098355882033</v>
+        <v>0.1129134437344788</v>
       </c>
       <c r="C89">
-        <v>8.915489076407564</v>
+        <v>8.677447687255022</v>
       </c>
       <c r="D89">
-        <v>33.39148907640757</v>
+        <v>33.43944768725503</v>
       </c>
       <c r="E89">
-        <v>12.182</v>
+        <v>12.468</v>
       </c>
       <c r="F89">
-        <v>24.882</v>
+        <v>25.168</v>
       </c>
       <c r="G89">
         <v>0.406</v>
@@ -8713,28 +8713,28 @@
         <v>4.91</v>
       </c>
       <c r="M89">
-        <v>1.5949362</v>
+        <v>1.6132688</v>
       </c>
       <c r="N89">
-        <v>3.3150638</v>
+        <v>3.2967312</v>
       </c>
       <c r="O89">
-        <v>0.66301276</v>
+        <v>0.6593462400000001</v>
       </c>
       <c r="P89">
-        <v>2.65205104</v>
+        <v>2.63738496</v>
       </c>
       <c r="Q89">
-        <v>7.342051039999999</v>
+        <v>7.32738496</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5261248891400254</v>
+        <v>0.5648920311206571</v>
       </c>
       <c r="T89">
-        <v>5.259754409691914</v>
+        <v>5.684270504098042</v>
       </c>
       <c r="U89">
         <v>0.0641</v>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>3.07849304567794</v>
+        <v>3.043510170158872</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1129134437344788</v>
+        <v>0.1128170518807544</v>
       </c>
       <c r="C90">
-        <v>8.677447687255022</v>
+        <v>8.439544257600019</v>
       </c>
       <c r="D90">
-        <v>33.43944768725503</v>
+        <v>33.48754425760002</v>
       </c>
       <c r="E90">
-        <v>12.468</v>
+        <v>12.754</v>
       </c>
       <c r="F90">
-        <v>25.168</v>
+        <v>25.454</v>
       </c>
       <c r="G90">
         <v>0.406</v>
@@ -8795,28 +8795,28 @@
         <v>4.91</v>
       </c>
       <c r="M90">
-        <v>1.6132688</v>
+        <v>1.6316014</v>
       </c>
       <c r="N90">
-        <v>3.2967312</v>
+        <v>3.2783986</v>
       </c>
       <c r="O90">
-        <v>0.6593462400000001</v>
+        <v>0.6556797200000001</v>
       </c>
       <c r="P90">
-        <v>2.63738496</v>
+        <v>2.62271888</v>
       </c>
       <c r="Q90">
-        <v>7.32738496</v>
+        <v>7.312718879999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5648920311206571</v>
+        <v>0.6107077443704945</v>
       </c>
       <c r="T90">
-        <v>5.684270504098042</v>
+        <v>6.185971342941647</v>
       </c>
       <c r="U90">
         <v>0.0641</v>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>3.043510170158872</v>
+        <v>3.009313426673941</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1128170518807544</v>
+        <v>0.1183366600270299</v>
       </c>
       <c r="C91">
-        <v>8.439544257600019</v>
+        <v>5.605341431413443</v>
       </c>
       <c r="D91">
-        <v>33.48754425760002</v>
+        <v>30.93934143141345</v>
       </c>
       <c r="E91">
-        <v>12.754</v>
+        <v>13.04</v>
       </c>
       <c r="F91">
-        <v>25.454</v>
+        <v>25.74</v>
       </c>
       <c r="G91">
         <v>0.406</v>
@@ -8877,45 +8877,45 @@
         <v>4.91</v>
       </c>
       <c r="M91">
-        <v>1.6316014</v>
+        <v>1.850706</v>
       </c>
       <c r="N91">
-        <v>3.2783986</v>
+        <v>3.059294</v>
       </c>
       <c r="O91">
-        <v>0.6556797200000001</v>
+        <v>0.6118588</v>
       </c>
       <c r="P91">
-        <v>2.62271888</v>
+        <v>2.4474352</v>
       </c>
       <c r="Q91">
-        <v>7.312718879999999</v>
+        <v>7.1374352</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.6107077443704945</v>
+        <v>0.6656866002702995</v>
       </c>
       <c r="T91">
-        <v>6.185971342941647</v>
+        <v>6.788012349553974</v>
       </c>
       <c r="U91">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V91">
         <v>0.2</v>
       </c>
       <c r="W91">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y91">
-        <v>3.009313426673941</v>
+        <v>2.653041596017952</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1183366600270299</v>
+        <v>0.1183026681733055</v>
       </c>
       <c r="C92">
-        <v>5.605341431413443</v>
+        <v>5.333846905415509</v>
       </c>
       <c r="D92">
-        <v>30.93934143141345</v>
+        <v>30.95384690541551</v>
       </c>
       <c r="E92">
-        <v>13.04</v>
+        <v>13.326</v>
       </c>
       <c r="F92">
-        <v>25.74</v>
+        <v>26.026</v>
       </c>
       <c r="G92">
         <v>0.406</v>
@@ -8959,28 +8959,28 @@
         <v>4.91</v>
       </c>
       <c r="M92">
-        <v>1.850706</v>
+        <v>1.8712694</v>
       </c>
       <c r="N92">
-        <v>3.059294</v>
+        <v>3.0387306</v>
       </c>
       <c r="O92">
-        <v>0.6118588</v>
+        <v>0.6077461200000001</v>
       </c>
       <c r="P92">
-        <v>2.4474352</v>
+        <v>2.43098448</v>
       </c>
       <c r="Q92">
-        <v>7.1374352</v>
+        <v>7.12098448</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6656866002702995</v>
+        <v>0.7328829797033942</v>
       </c>
       <c r="T92">
-        <v>6.788012349553974</v>
+        <v>7.523840246524595</v>
       </c>
       <c r="U92">
         <v>0.07190000000000001</v>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.653041596017952</v>
+        <v>2.623887292765007</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1183026681733055</v>
+        <v>0.118268676319581</v>
       </c>
       <c r="C93">
-        <v>5.333846905415509</v>
+        <v>5.062365987171297</v>
       </c>
       <c r="D93">
-        <v>30.95384690541551</v>
+        <v>30.9683659871713</v>
       </c>
       <c r="E93">
-        <v>13.326</v>
+        <v>13.612</v>
       </c>
       <c r="F93">
-        <v>26.026</v>
+        <v>26.312</v>
       </c>
       <c r="G93">
         <v>0.406</v>
@@ -9041,28 +9041,28 @@
         <v>4.91</v>
       </c>
       <c r="M93">
-        <v>1.8712694</v>
+        <v>1.8918328</v>
       </c>
       <c r="N93">
-        <v>3.0387306</v>
+        <v>3.0181672</v>
       </c>
       <c r="O93">
-        <v>0.6077461200000001</v>
+        <v>0.60363344</v>
       </c>
       <c r="P93">
-        <v>2.43098448</v>
+        <v>2.41453376</v>
       </c>
       <c r="Q93">
-        <v>7.12098448</v>
+        <v>7.104533759999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7328829797033942</v>
+        <v>0.816878453994763</v>
       </c>
       <c r="T93">
-        <v>7.523840246524595</v>
+        <v>8.443625117737874</v>
       </c>
       <c r="U93">
         <v>0.07190000000000001</v>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.623887292765007</v>
+        <v>2.595366778713214</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.118268676319581</v>
+        <v>0.1182346844658566</v>
       </c>
       <c r="C94">
-        <v>5.062365987171297</v>
+        <v>4.790898695838202</v>
       </c>
       <c r="D94">
-        <v>30.9683659871713</v>
+        <v>30.98289869583821</v>
       </c>
       <c r="E94">
-        <v>13.612</v>
+        <v>13.898</v>
       </c>
       <c r="F94">
-        <v>26.312</v>
+        <v>26.598</v>
       </c>
       <c r="G94">
         <v>0.406</v>
@@ -9123,28 +9123,28 @@
         <v>4.91</v>
       </c>
       <c r="M94">
-        <v>1.8918328</v>
+        <v>1.9123962</v>
       </c>
       <c r="N94">
-        <v>3.0181672</v>
+        <v>2.9976038</v>
       </c>
       <c r="O94">
-        <v>0.60363344</v>
+        <v>0.59952076</v>
       </c>
       <c r="P94">
-        <v>2.41453376</v>
+        <v>2.39808304</v>
       </c>
       <c r="Q94">
-        <v>7.104533759999999</v>
+        <v>7.088083039999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.816878453994763</v>
+        <v>0.9248726352265226</v>
       </c>
       <c r="T94">
-        <v>8.443625117737874</v>
+        <v>9.626205666440658</v>
       </c>
       <c r="U94">
         <v>0.07190000000000001</v>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.595366778713214</v>
+        <v>2.567459609049631</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1182346844658566</v>
+        <v>0.1182006926121321</v>
       </c>
       <c r="C95">
-        <v>4.790898695838202</v>
+        <v>4.519445050609569</v>
       </c>
       <c r="D95">
-        <v>30.98289869583821</v>
+        <v>30.99744505060957</v>
       </c>
       <c r="E95">
-        <v>13.898</v>
+        <v>14.184</v>
       </c>
       <c r="F95">
-        <v>26.598</v>
+        <v>26.884</v>
       </c>
       <c r="G95">
         <v>0.406</v>
@@ -9205,28 +9205,28 @@
         <v>4.91</v>
       </c>
       <c r="M95">
-        <v>1.9123962</v>
+        <v>1.9329596</v>
       </c>
       <c r="N95">
-        <v>2.9976038</v>
+        <v>2.9770404</v>
       </c>
       <c r="O95">
-        <v>0.59952076</v>
+        <v>0.59540808</v>
       </c>
       <c r="P95">
-        <v>2.39808304</v>
+        <v>2.38163232</v>
       </c>
       <c r="Q95">
-        <v>7.088083039999999</v>
+        <v>7.071632319999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9248726352265226</v>
+        <v>1.068864876868869</v>
       </c>
       <c r="T95">
-        <v>9.626205666440658</v>
+        <v>11.2029797313777</v>
       </c>
       <c r="U95">
         <v>0.07190000000000001</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.567459609049631</v>
+        <v>2.540146208953358</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1182006926121321</v>
+        <v>0.1181667007584076</v>
       </c>
       <c r="C96">
-        <v>4.519445050609569</v>
+        <v>4.248005070714807</v>
       </c>
       <c r="D96">
-        <v>30.99744505060957</v>
+        <v>31.01200507071481</v>
       </c>
       <c r="E96">
-        <v>14.184</v>
+        <v>14.47</v>
       </c>
       <c r="F96">
-        <v>26.884</v>
+        <v>27.17</v>
       </c>
       <c r="G96">
         <v>0.406</v>
@@ -9287,28 +9287,28 @@
         <v>4.91</v>
       </c>
       <c r="M96">
-        <v>1.9329596</v>
+        <v>1.953523</v>
       </c>
       <c r="N96">
-        <v>2.9770404</v>
+        <v>2.956477</v>
       </c>
       <c r="O96">
-        <v>0.59540808</v>
+        <v>0.5912953999999999</v>
       </c>
       <c r="P96">
-        <v>2.38163232</v>
+        <v>2.3651816</v>
       </c>
       <c r="Q96">
-        <v>7.071632319999999</v>
+        <v>7.055181599999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.068864876868869</v>
+        <v>1.270454015168154</v>
       </c>
       <c r="T96">
-        <v>11.2029797313777</v>
+        <v>13.41046342228958</v>
       </c>
       <c r="U96">
         <v>0.07190000000000001</v>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.540146208953358</v>
+        <v>2.51340782780648</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1181667007584076</v>
+        <v>0.1211279089046832</v>
       </c>
       <c r="C97">
-        <v>4.248005070714807</v>
+        <v>2.742895136786597</v>
       </c>
       <c r="D97">
-        <v>31.01200507071481</v>
+        <v>29.7928951367866</v>
       </c>
       <c r="E97">
-        <v>14.47</v>
+        <v>14.756</v>
       </c>
       <c r="F97">
-        <v>27.17</v>
+        <v>27.456</v>
       </c>
       <c r="G97">
         <v>0.406</v>
@@ -9369,45 +9369,45 @@
         <v>4.91</v>
       </c>
       <c r="M97">
-        <v>1.953523</v>
+        <v>2.0811648</v>
       </c>
       <c r="N97">
-        <v>2.956477</v>
+        <v>2.8288352</v>
       </c>
       <c r="O97">
-        <v>0.5912953999999999</v>
+        <v>0.56576704</v>
       </c>
       <c r="P97">
-        <v>2.3651816</v>
+        <v>2.26306816</v>
       </c>
       <c r="Q97">
-        <v>7.055181599999999</v>
+        <v>6.953068159999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.270454015168154</v>
+        <v>1.572837722617082</v>
       </c>
       <c r="T97">
-        <v>13.41046342228958</v>
+        <v>16.72168895865738</v>
       </c>
       <c r="U97">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V97">
         <v>0.2</v>
       </c>
       <c r="W97">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y97">
-        <v>2.51340782780648</v>
+        <v>2.3592557398626</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1211279089046832</v>
+        <v>0.1211251170509587</v>
       </c>
       <c r="C98">
-        <v>2.742895136786601</v>
+        <v>2.457999382070334</v>
       </c>
       <c r="D98">
-        <v>29.7928951367866</v>
+        <v>29.79399938207034</v>
       </c>
       <c r="E98">
-        <v>14.756</v>
+        <v>15.042</v>
       </c>
       <c r="F98">
-        <v>27.456</v>
+        <v>27.742</v>
       </c>
       <c r="G98">
         <v>0.406</v>
@@ -9451,28 +9451,28 @@
         <v>4.91</v>
       </c>
       <c r="M98">
-        <v>2.0811648</v>
+        <v>2.1028436</v>
       </c>
       <c r="N98">
-        <v>2.8288352</v>
+        <v>2.8071564</v>
       </c>
       <c r="O98">
-        <v>0.56576704</v>
+        <v>0.56143128</v>
       </c>
       <c r="P98">
-        <v>2.26306816</v>
+        <v>2.24572512</v>
       </c>
       <c r="Q98">
-        <v>6.953068159999999</v>
+        <v>6.935725119999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.572837722617078</v>
+        <v>2.076810568365288</v>
       </c>
       <c r="T98">
-        <v>16.72168895865734</v>
+        <v>22.24039818593698</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.3592557398626</v>
+        <v>2.334933515740305</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1211251170509587</v>
+        <v>0.1211223251972342</v>
       </c>
       <c r="C99">
-        <v>2.457999382070334</v>
+        <v>2.1731037092127</v>
       </c>
       <c r="D99">
-        <v>29.79399938207034</v>
+        <v>29.7951037092127</v>
       </c>
       <c r="E99">
-        <v>15.042</v>
+        <v>15.328</v>
       </c>
       <c r="F99">
-        <v>27.742</v>
+        <v>28.028</v>
       </c>
       <c r="G99">
         <v>0.406</v>
@@ -9533,28 +9533,28 @@
         <v>4.91</v>
       </c>
       <c r="M99">
-        <v>2.1028436</v>
+        <v>2.1245224</v>
       </c>
       <c r="N99">
-        <v>2.8071564</v>
+        <v>2.7854776</v>
       </c>
       <c r="O99">
-        <v>0.56143128</v>
+        <v>0.55709552</v>
       </c>
       <c r="P99">
-        <v>2.24572512</v>
+        <v>2.22838208</v>
       </c>
       <c r="Q99">
-        <v>6.935725119999999</v>
+        <v>6.918382079999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.076810568365288</v>
+        <v>3.084756259861709</v>
       </c>
       <c r="T99">
-        <v>22.24039818593698</v>
+        <v>33.27781664049628</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.334933515740305</v>
+        <v>2.311107663538873</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1211223251972342</v>
+        <v>0.1211195333435097</v>
       </c>
       <c r="C100">
-        <v>2.1731037092127</v>
+        <v>1.888208118222813</v>
       </c>
       <c r="D100">
-        <v>29.7951037092127</v>
+        <v>29.79620811822281</v>
       </c>
       <c r="E100">
-        <v>15.328</v>
+        <v>15.614</v>
       </c>
       <c r="F100">
-        <v>28.028</v>
+        <v>28.314</v>
       </c>
       <c r="G100">
         <v>0.406</v>
@@ -9615,28 +9615,28 @@
         <v>4.91</v>
       </c>
       <c r="M100">
-        <v>2.1245224</v>
+        <v>2.1462012</v>
       </c>
       <c r="N100">
-        <v>2.7854776</v>
+        <v>2.7637988</v>
       </c>
       <c r="O100">
-        <v>0.55709552</v>
+        <v>0.55275976</v>
       </c>
       <c r="P100">
-        <v>2.22838208</v>
+        <v>2.21103904</v>
       </c>
       <c r="Q100">
-        <v>6.918382079999999</v>
+        <v>6.90103904</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.084756259861709</v>
+        <v>6.10859333435097</v>
       </c>
       <c r="T100">
-        <v>33.27781664049628</v>
+        <v>66.39007200417416</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.311107663538873</v>
+        <v>2.287763141684946</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1211195333435097</v>
-      </c>
-      <c r="C101">
-        <v>1.888208118222813</v>
-      </c>
-      <c r="D101">
-        <v>29.79620811822281</v>
-      </c>
-      <c r="E101">
-        <v>15.614</v>
-      </c>
-      <c r="F101">
-        <v>28.314</v>
-      </c>
-      <c r="G101">
-        <v>0.406</v>
-      </c>
-      <c r="H101">
-        <v>15.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>9.6</v>
-      </c>
-      <c r="K101">
-        <v>4.69</v>
-      </c>
-      <c r="L101">
-        <v>4.91</v>
-      </c>
-      <c r="M101">
-        <v>2.1462012</v>
-      </c>
-      <c r="N101">
-        <v>2.7637988</v>
-      </c>
-      <c r="O101">
-        <v>0.55275976</v>
-      </c>
-      <c r="P101">
-        <v>2.21103904</v>
-      </c>
-      <c r="Q101">
-        <v>6.90103904</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.10859333435097</v>
-      </c>
-      <c r="T101">
-        <v>66.39007200417416</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.2</v>
-      </c>
-      <c r="W101">
-        <v>0.06064000000000001</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.287763141684946</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
